--- a/2- BB.DD. SERVICIOS Y UNIDADES/BBDD SERVICIOS Y UNIDADES.xlsx
+++ b/2- BB.DD. SERVICIOS Y UNIDADES/BBDD SERVICIOS Y UNIDADES.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\IPLACEX\Año 2\PRÁCTICA IPLACEX\PLATAFORMA PASANTÍAS\GITHUB\2- BB.DD. SERVICIOS Y UNIDADES\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{860AAC2D-A1CF-4916-B290-AA68AB301A18}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{906C785C-3FFB-4E84-98D4-6C6496983217}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-28920" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{7936E908-9EDA-4102-87A8-C4382552261F}"/>
   </bookViews>
@@ -39,14 +39,11 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="7" uniqueCount="7">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="236" uniqueCount="172">
   <si>
     <t>id</t>
   </si>
   <si>
-    <t>servicio/unidad</t>
-  </si>
-  <si>
     <t>jefatura</t>
   </si>
   <si>
@@ -60,6 +57,504 @@
   </si>
   <si>
     <t>timestamp</t>
+  </si>
+  <si>
+    <t>dra. carolina mendez benavente </t>
+  </si>
+  <si>
+    <t>carolina.mendezb@redsalud.gob.cl</t>
+  </si>
+  <si>
+    <t>jessica pino </t>
+  </si>
+  <si>
+    <t>jessica.pinoa@redsalud.gob.cl</t>
+  </si>
+  <si>
+    <t>dr. andres readi sakurada</t>
+  </si>
+  <si>
+    <t>andres.readi@redsalud.gob.cl</t>
+  </si>
+  <si>
+    <t>alicia cutipa </t>
+  </si>
+  <si>
+    <t>alicia.cutipa@redsalud.gob.cl</t>
+  </si>
+  <si>
+    <t>maria.hevia@redsalud.gob.cl</t>
+  </si>
+  <si>
+    <t>jennifer luengo</t>
+  </si>
+  <si>
+    <t>jennifer.luengo@redsalud.gob.cl</t>
+  </si>
+  <si>
+    <t>marcia.lopeza@redsalud.gob.cl</t>
+  </si>
+  <si>
+    <t>maria isabel ortiz</t>
+  </si>
+  <si>
+    <t>mariaisabel.ortiz@redsalud.gob.cl</t>
+  </si>
+  <si>
+    <t>felipesantiba@gmail.com</t>
+  </si>
+  <si>
+    <t>claudia reyes</t>
+  </si>
+  <si>
+    <t>claudia.reyes.c@redsalud.gob.cl</t>
+  </si>
+  <si>
+    <t>dr. carlos iturriaga villarroel</t>
+  </si>
+  <si>
+    <t>carlos.iturriaga@redsalud.gob.cl</t>
+  </si>
+  <si>
+    <t>katherine iturra</t>
+  </si>
+  <si>
+    <t>katherine.iturra@redsalud.gob.cl</t>
+  </si>
+  <si>
+    <t>dr. juan stambuk mayorga</t>
+  </si>
+  <si>
+    <t>juanstambuk@gmail.com</t>
+  </si>
+  <si>
+    <t>maria jose abarca</t>
+  </si>
+  <si>
+    <t>mariajose.abarca@redsalud.gob.cl</t>
+  </si>
+  <si>
+    <t>dra. patricia vásquez toriello </t>
+  </si>
+  <si>
+    <t>patricia.vasquez@redsalud.gob.cl</t>
+  </si>
+  <si>
+    <t>jacqueline cortes</t>
+  </si>
+  <si>
+    <t>jacqueline.cortes@redsalud.gob.cl</t>
+  </si>
+  <si>
+    <t>apuentescdt@yahoo.com</t>
+  </si>
+  <si>
+    <t>maria isabel robles</t>
+  </si>
+  <si>
+    <t>mariaisabel.robles@redsalud.gob.cl</t>
+  </si>
+  <si>
+    <t>dr. hugo gonzález betoni</t>
+  </si>
+  <si>
+    <t>hugo.gonzalezd@redsalud.gob.cl</t>
+  </si>
+  <si>
+    <t>sandra silva</t>
+  </si>
+  <si>
+    <t>sandra.silva@redsalud.gob.cl</t>
+  </si>
+  <si>
+    <t>dra. sandra aranda bazaez</t>
+  </si>
+  <si>
+    <t>sandra.arandab@redsalud.gob.cl</t>
+  </si>
+  <si>
+    <t>no aplica</t>
+  </si>
+  <si>
+    <t>dr. luis vicencio villaseca</t>
+  </si>
+  <si>
+    <t>luis.vicencio@redsalud.gob.cl</t>
+  </si>
+  <si>
+    <t>maria cristina alvarez</t>
+  </si>
+  <si>
+    <t>mcristina.alvarez@redsalud.gob.cl</t>
+  </si>
+  <si>
+    <t>dra. camila riquelme jara</t>
+  </si>
+  <si>
+    <t>camila.riquelmej@redsalud.gob.cl</t>
+  </si>
+  <si>
+    <t>marisol carrera</t>
+  </si>
+  <si>
+    <t>marisol.carrera@redsalud.gob.cl</t>
+  </si>
+  <si>
+    <t>dr. david gallardo perez</t>
+  </si>
+  <si>
+    <t>doborque@gmail.com</t>
+  </si>
+  <si>
+    <t>procuramiento y trasplante</t>
+  </si>
+  <si>
+    <t>jmpalaciosj50@gmail.com</t>
+  </si>
+  <si>
+    <t>servicio chacabuco</t>
+  </si>
+  <si>
+    <t>dra. tamara carrasco muñoz</t>
+  </si>
+  <si>
+    <t>tamara.carrasco@redsalud.gob.cl</t>
+  </si>
+  <si>
+    <t>servicio médico-quirúrgico</t>
+  </si>
+  <si>
+    <t>dra. solange valenzuela valenzuela</t>
+  </si>
+  <si>
+    <t>solange.valenzuela@redsalud.gob.cl</t>
+  </si>
+  <si>
+    <t>dra. maría del pilar hevia juricic</t>
+  </si>
+  <si>
+    <t>dra. marcia lopez aceitón</t>
+  </si>
+  <si>
+    <t>dr. felipe santibáñez galvez</t>
+  </si>
+  <si>
+    <t>dr. ángel puentes rico</t>
+  </si>
+  <si>
+    <t>dr. josé manuel palacios junemann</t>
+  </si>
+  <si>
+    <t>cr. ambulatorio</t>
+  </si>
+  <si>
+    <t>srta. lya reyes carreño</t>
+  </si>
+  <si>
+    <t>lya.reyes@redsalud.gob.cl</t>
+  </si>
+  <si>
+    <t>eficiencia clínica hospitalaria</t>
+  </si>
+  <si>
+    <t>mat. katherinne kupferschmidt silva</t>
+  </si>
+  <si>
+    <t>katherinne.kupferschmidt@redsalud.gob.cl</t>
+  </si>
+  <si>
+    <t>mat. claudia neira</t>
+  </si>
+  <si>
+    <t>claudia.neira@redsalud.gob.cl</t>
+  </si>
+  <si>
+    <t>gestión de la demanda</t>
+  </si>
+  <si>
+    <t>eu. ana karina henriquez zamorano</t>
+  </si>
+  <si>
+    <t>anakarina.henriquez@redsalud.gob.cl</t>
+  </si>
+  <si>
+    <t>gestión de pacientes</t>
+  </si>
+  <si>
+    <t>eu. valesska gonzalez toro</t>
+  </si>
+  <si>
+    <t>valesska.gonzalez@redsalud.gob.cl</t>
+  </si>
+  <si>
+    <t>pendiente</t>
+  </si>
+  <si>
+    <t>dr. óscar loureiro caldera</t>
+  </si>
+  <si>
+    <t>doctorloureiro@gmail.com</t>
+  </si>
+  <si>
+    <t>monica torres</t>
+  </si>
+  <si>
+    <t>monica.torresc@redsalud.gob.cl</t>
+  </si>
+  <si>
+    <t>dra. cynthia margarit segura</t>
+  </si>
+  <si>
+    <t>cynthia.margarit@redsalud.gob.cl</t>
+  </si>
+  <si>
+    <t>claudia vicencio</t>
+  </si>
+  <si>
+    <t>claudia.vicencio@redsalud.gob.cl</t>
+  </si>
+  <si>
+    <t>dr. felipe morera sánchez</t>
+  </si>
+  <si>
+    <t>fmorerasanchez@yahoo.com</t>
+  </si>
+  <si>
+    <t>pamela jara (tecnologo encargada)</t>
+  </si>
+  <si>
+    <t>pamela.jara@redsalud.gob.cl</t>
+  </si>
+  <si>
+    <t>dra. catalina cisternas pinto</t>
+  </si>
+  <si>
+    <t>catalina.cisternas@redsalud.gob.cl</t>
+  </si>
+  <si>
+    <t>patricia arancibia</t>
+  </si>
+  <si>
+    <t>patricia.arancibia@redsalud.gob.cl</t>
+  </si>
+  <si>
+    <t>dra. roxana fuentes cartes</t>
+  </si>
+  <si>
+    <t>roxana.fuentes@redsalud.gob.cl</t>
+  </si>
+  <si>
+    <t>dra. soledad bertoló pérez</t>
+  </si>
+  <si>
+    <t>soledad.bertolo@redsalud.gob.cl</t>
+  </si>
+  <si>
+    <t>erika carquin</t>
+  </si>
+  <si>
+    <t>erika.carquin@redsalud.gob.cl</t>
+  </si>
+  <si>
+    <t>dr. félix vásquez rodríguez</t>
+  </si>
+  <si>
+    <t>felix.vasquezr@yahoo.com</t>
+  </si>
+  <si>
+    <t>medicina</t>
+  </si>
+  <si>
+    <t>dra. marta quiroz trujillo</t>
+  </si>
+  <si>
+    <t>marta.quiroz@redsalud.gob.cl</t>
+  </si>
+  <si>
+    <t>teresa salazar</t>
+  </si>
+  <si>
+    <t>teresa.salazar@redsalud.gob.cl</t>
+  </si>
+  <si>
+    <t>dra. catalina gutiérrez ruiz</t>
+  </si>
+  <si>
+    <t>catalina.gutierrez@redsalud,gob.cl</t>
+  </si>
+  <si>
+    <t>sandra amestica</t>
+  </si>
+  <si>
+    <t>sandra.amestica@redsalud.gob.cl</t>
+  </si>
+  <si>
+    <t>pediatría</t>
+  </si>
+  <si>
+    <t>dr. josé perillán torres</t>
+  </si>
+  <si>
+    <t>joseperillan@gmail.com</t>
+  </si>
+  <si>
+    <t>jannett madrid</t>
+  </si>
+  <si>
+    <t>jannett.madrid@redsalud.gob.cl</t>
+  </si>
+  <si>
+    <t>dr. gabriel núñez tome</t>
+  </si>
+  <si>
+    <t>lgnunezt@gmail.com</t>
+  </si>
+  <si>
+    <t>rosario castillo</t>
+  </si>
+  <si>
+    <t>rosario.castilloj@redsalud.gob.cl</t>
+  </si>
+  <si>
+    <t>flga. valentina román</t>
+  </si>
+  <si>
+    <t>valentina.roman.m@redsalud.gob.cl</t>
+  </si>
+  <si>
+    <t>rosa soto</t>
+  </si>
+  <si>
+    <t>rosa.soto@redsalud.gob.cl</t>
+  </si>
+  <si>
+    <t>dr. marcos estica rivas</t>
+  </si>
+  <si>
+    <t>marcos.estica@redsalud.gob.cl</t>
+  </si>
+  <si>
+    <t>myriam figueroa</t>
+  </si>
+  <si>
+    <t>myriam.figueroa@redsalud.gob.cl</t>
+  </si>
+  <si>
+    <t>dra. cecilia trejo rojas</t>
+  </si>
+  <si>
+    <t>cecilia.trejo@redsalud.gob.cl</t>
+  </si>
+  <si>
+    <t>marlene donoso</t>
+  </si>
+  <si>
+    <t>marlene.donoso@redsalud.gob.cl</t>
+  </si>
+  <si>
+    <t>some</t>
+  </si>
+  <si>
+    <t>eu. daniela calderon avendaño</t>
+  </si>
+  <si>
+    <t>daniela.calderon@redsalud.gob.cl</t>
+  </si>
+  <si>
+    <t>maritza malhue</t>
+  </si>
+  <si>
+    <t>maritza.malhue@redsalud.gob.cl</t>
+  </si>
+  <si>
+    <t>subdirección</t>
+  </si>
+  <si>
+    <t>médica</t>
+  </si>
+  <si>
+    <t>policlínico gastroenterología</t>
+  </si>
+  <si>
+    <t>policlínico neuropsiquiatria infantil</t>
+  </si>
+  <si>
+    <t>policlínico oftalmología</t>
+  </si>
+  <si>
+    <t>policlínico odontología</t>
+  </si>
+  <si>
+    <t>policlínico broncopulmonar</t>
+  </si>
+  <si>
+    <t>policlínico dermatología</t>
+  </si>
+  <si>
+    <t>policlínico endocrinología</t>
+  </si>
+  <si>
+    <t>policlínico medicina</t>
+  </si>
+  <si>
+    <t>policlínico infectología</t>
+  </si>
+  <si>
+    <t>policlínico pediatría</t>
+  </si>
+  <si>
+    <t>policlínico nefrología</t>
+  </si>
+  <si>
+    <t>policlínico medicina física y rehabilitación</t>
+  </si>
+  <si>
+    <t>policlínico diabetes</t>
+  </si>
+  <si>
+    <t>policlínico reumatología</t>
+  </si>
+  <si>
+    <t>policlínico neurología adulto</t>
+  </si>
+  <si>
+    <t>gestión de los cuidados de matronería</t>
+  </si>
+  <si>
+    <t>neonatología</t>
+  </si>
+  <si>
+    <t>otorrinolaringología</t>
+  </si>
+  <si>
+    <t>obstetricia y ginecología</t>
+  </si>
+  <si>
+    <t>pabellones</t>
+  </si>
+  <si>
+    <t>urología</t>
+  </si>
+  <si>
+    <t>cirugía </t>
+  </si>
+  <si>
+    <t>enfermedades cardiovasculares</t>
+  </si>
+  <si>
+    <t>u.p.c adulto</t>
+  </si>
+  <si>
+    <t>hemato-oncología</t>
+  </si>
+  <si>
+    <t>urgencia adulto</t>
+  </si>
+  <si>
+    <t>hospitalizacion domiciliaria</t>
+  </si>
+  <si>
+    <t>servicio/unidad/cr</t>
   </si>
 </sst>
 </file>
@@ -75,12 +570,18 @@
       <scheme val="minor"/>
     </font>
   </fonts>
-  <fills count="2">
+  <fills count="3">
     <fill>
       <patternFill patternType="none"/>
     </fill>
     <fill>
       <patternFill patternType="gray125"/>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFFF00"/>
+        <bgColor indexed="64"/>
+      </patternFill>
     </fill>
   </fills>
   <borders count="1">
@@ -95,8 +596,9 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="1">
+  <cellXfs count="2">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="0" xfId="0" applyFill="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -431,30 +933,911 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{37800E50-6288-4855-903E-7D1C9ED078D0}">
-  <dimension ref="A1:G1"/>
+  <dimension ref="A1:H39"/>
   <sheetFormatPr baseColWidth="10" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <cols>
+    <col min="1" max="1" width="3" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="34.140625" customWidth="1"/>
+  </cols>
   <sheetData>
-    <row r="1" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A1" t="s">
         <v>0</v>
       </c>
       <c r="B1" t="s">
+        <v>142</v>
+      </c>
+      <c r="C1" t="s">
+        <v>171</v>
+      </c>
+      <c r="D1" t="s">
         <v>1</v>
       </c>
-      <c r="C1" t="s">
+      <c r="E1" t="s">
         <v>2</v>
       </c>
-      <c r="D1" t="s">
+      <c r="F1" t="s">
         <v>3</v>
       </c>
-      <c r="E1" t="s">
+      <c r="G1" t="s">
         <v>4</v>
       </c>
-      <c r="F1" t="s">
+      <c r="H1" t="s">
         <v>5</v>
       </c>
-      <c r="G1" t="s">
+    </row>
+    <row r="2" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A2">
+        <v>1</v>
+      </c>
+      <c r="B2" t="s">
+        <v>143</v>
+      </c>
+      <c r="C2" t="s">
+        <v>160</v>
+      </c>
+      <c r="D2" t="s">
         <v>6</v>
+      </c>
+      <c r="E2" t="s">
+        <v>7</v>
+      </c>
+      <c r="F2" t="s">
+        <v>8</v>
+      </c>
+      <c r="G2" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="3" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A3">
+        <v>2</v>
+      </c>
+      <c r="B3" t="s">
+        <v>143</v>
+      </c>
+      <c r="C3" t="s">
+        <v>161</v>
+      </c>
+      <c r="D3" t="s">
+        <v>10</v>
+      </c>
+      <c r="E3" t="s">
+        <v>11</v>
+      </c>
+      <c r="F3" t="s">
+        <v>12</v>
+      </c>
+      <c r="G3" t="s">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="4" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A4">
+        <v>3</v>
+      </c>
+      <c r="B4" t="s">
+        <v>143</v>
+      </c>
+      <c r="C4" t="s">
+        <v>116</v>
+      </c>
+      <c r="D4" t="s">
+        <v>63</v>
+      </c>
+      <c r="E4" t="s">
+        <v>14</v>
+      </c>
+      <c r="F4" t="s">
+        <v>15</v>
+      </c>
+      <c r="G4" t="s">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="5" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A5">
+        <v>4</v>
+      </c>
+      <c r="B5" t="s">
+        <v>143</v>
+      </c>
+      <c r="C5" t="s">
+        <v>162</v>
+      </c>
+      <c r="D5" t="s">
+        <v>64</v>
+      </c>
+      <c r="E5" t="s">
+        <v>17</v>
+      </c>
+      <c r="F5" t="s">
+        <v>18</v>
+      </c>
+      <c r="G5" t="s">
+        <v>19</v>
+      </c>
+    </row>
+    <row r="6" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A6">
+        <v>5</v>
+      </c>
+      <c r="B6" t="s">
+        <v>143</v>
+      </c>
+      <c r="C6" t="s">
+        <v>163</v>
+      </c>
+      <c r="D6" t="s">
+        <v>65</v>
+      </c>
+      <c r="E6" t="s">
+        <v>20</v>
+      </c>
+      <c r="F6" t="s">
+        <v>21</v>
+      </c>
+      <c r="G6" t="s">
+        <v>22</v>
+      </c>
+    </row>
+    <row r="7" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A7">
+        <v>6</v>
+      </c>
+      <c r="B7" t="s">
+        <v>143</v>
+      </c>
+      <c r="C7" t="s">
+        <v>164</v>
+      </c>
+      <c r="D7" t="s">
+        <v>23</v>
+      </c>
+      <c r="E7" t="s">
+        <v>24</v>
+      </c>
+      <c r="F7" t="s">
+        <v>25</v>
+      </c>
+      <c r="G7" t="s">
+        <v>26</v>
+      </c>
+    </row>
+    <row r="8" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A8">
+        <v>7</v>
+      </c>
+      <c r="B8" t="s">
+        <v>143</v>
+      </c>
+      <c r="C8" t="s">
+        <v>165</v>
+      </c>
+      <c r="D8" t="s">
+        <v>27</v>
+      </c>
+      <c r="E8" t="s">
+        <v>28</v>
+      </c>
+      <c r="F8" t="s">
+        <v>29</v>
+      </c>
+      <c r="G8" t="s">
+        <v>30</v>
+      </c>
+    </row>
+    <row r="9" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A9">
+        <v>8</v>
+      </c>
+      <c r="B9" t="s">
+        <v>143</v>
+      </c>
+      <c r="C9" t="s">
+        <v>107</v>
+      </c>
+      <c r="D9" t="s">
+        <v>31</v>
+      </c>
+      <c r="E9" t="s">
+        <v>32</v>
+      </c>
+      <c r="F9" t="s">
+        <v>33</v>
+      </c>
+      <c r="G9" t="s">
+        <v>34</v>
+      </c>
+    </row>
+    <row r="10" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A10">
+        <v>9</v>
+      </c>
+      <c r="B10" t="s">
+        <v>143</v>
+      </c>
+      <c r="C10" t="s">
+        <v>166</v>
+      </c>
+      <c r="D10" t="s">
+        <v>66</v>
+      </c>
+      <c r="E10" t="s">
+        <v>35</v>
+      </c>
+      <c r="F10" t="s">
+        <v>36</v>
+      </c>
+      <c r="G10" t="s">
+        <v>37</v>
+      </c>
+    </row>
+    <row r="11" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A11">
+        <v>10</v>
+      </c>
+      <c r="B11" t="s">
+        <v>143</v>
+      </c>
+      <c r="C11" t="s">
+        <v>167</v>
+      </c>
+      <c r="D11" t="s">
+        <v>38</v>
+      </c>
+      <c r="E11" t="s">
+        <v>39</v>
+      </c>
+      <c r="F11" t="s">
+        <v>40</v>
+      </c>
+      <c r="G11" t="s">
+        <v>41</v>
+      </c>
+    </row>
+    <row r="12" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A12">
+        <v>11</v>
+      </c>
+      <c r="B12" t="s">
+        <v>143</v>
+      </c>
+      <c r="C12" t="s">
+        <v>168</v>
+      </c>
+      <c r="D12" t="s">
+        <v>42</v>
+      </c>
+      <c r="E12" t="s">
+        <v>43</v>
+      </c>
+      <c r="F12" s="1" t="s">
+        <v>82</v>
+      </c>
+      <c r="G12" s="1" t="s">
+        <v>82</v>
+      </c>
+    </row>
+    <row r="13" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A13">
+        <v>12</v>
+      </c>
+      <c r="B13" t="s">
+        <v>143</v>
+      </c>
+      <c r="C13" t="s">
+        <v>169</v>
+      </c>
+      <c r="D13" t="s">
+        <v>45</v>
+      </c>
+      <c r="E13" t="s">
+        <v>46</v>
+      </c>
+      <c r="F13" t="s">
+        <v>47</v>
+      </c>
+      <c r="G13" t="s">
+        <v>48</v>
+      </c>
+    </row>
+    <row r="14" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A14">
+        <v>13</v>
+      </c>
+      <c r="B14" t="s">
+        <v>143</v>
+      </c>
+      <c r="C14" t="s">
+        <v>170</v>
+      </c>
+      <c r="D14" t="s">
+        <v>49</v>
+      </c>
+      <c r="E14" t="s">
+        <v>50</v>
+      </c>
+      <c r="F14" t="s">
+        <v>51</v>
+      </c>
+      <c r="G14" t="s">
+        <v>52</v>
+      </c>
+    </row>
+    <row r="15" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A15">
+        <v>14</v>
+      </c>
+      <c r="B15" t="s">
+        <v>143</v>
+      </c>
+      <c r="C15" t="s">
+        <v>79</v>
+      </c>
+      <c r="D15" t="s">
+        <v>53</v>
+      </c>
+      <c r="E15" t="s">
+        <v>54</v>
+      </c>
+      <c r="F15" t="s">
+        <v>44</v>
+      </c>
+      <c r="G15" t="s">
+        <v>44</v>
+      </c>
+    </row>
+    <row r="16" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A16">
+        <v>15</v>
+      </c>
+      <c r="B16" t="s">
+        <v>143</v>
+      </c>
+      <c r="C16" t="s">
+        <v>55</v>
+      </c>
+      <c r="D16" t="s">
+        <v>67</v>
+      </c>
+      <c r="E16" t="s">
+        <v>56</v>
+      </c>
+      <c r="F16" t="s">
+        <v>44</v>
+      </c>
+      <c r="G16" t="s">
+        <v>44</v>
+      </c>
+    </row>
+    <row r="17" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A17">
+        <v>16</v>
+      </c>
+      <c r="B17" t="s">
+        <v>143</v>
+      </c>
+      <c r="C17" t="s">
+        <v>57</v>
+      </c>
+      <c r="D17" t="s">
+        <v>58</v>
+      </c>
+      <c r="E17" t="s">
+        <v>59</v>
+      </c>
+      <c r="F17" t="s">
+        <v>44</v>
+      </c>
+      <c r="G17" t="s">
+        <v>44</v>
+      </c>
+    </row>
+    <row r="18" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A18">
+        <v>17</v>
+      </c>
+      <c r="B18" t="s">
+        <v>143</v>
+      </c>
+      <c r="C18" t="s">
+        <v>60</v>
+      </c>
+      <c r="D18" t="s">
+        <v>61</v>
+      </c>
+      <c r="E18" t="s">
+        <v>62</v>
+      </c>
+      <c r="F18" s="1" t="s">
+        <v>82</v>
+      </c>
+      <c r="G18" s="1" t="s">
+        <v>82</v>
+      </c>
+    </row>
+    <row r="19" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A19">
+        <v>18</v>
+      </c>
+      <c r="B19" t="s">
+        <v>143</v>
+      </c>
+      <c r="C19" t="s">
+        <v>68</v>
+      </c>
+      <c r="D19" t="s">
+        <v>69</v>
+      </c>
+      <c r="E19" t="s">
+        <v>70</v>
+      </c>
+      <c r="F19" t="s">
+        <v>44</v>
+      </c>
+      <c r="G19" t="s">
+        <v>44</v>
+      </c>
+    </row>
+    <row r="20" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A20">
+        <v>19</v>
+      </c>
+      <c r="B20" t="s">
+        <v>143</v>
+      </c>
+      <c r="C20" t="s">
+        <v>71</v>
+      </c>
+      <c r="D20" t="s">
+        <v>72</v>
+      </c>
+      <c r="E20" t="s">
+        <v>73</v>
+      </c>
+      <c r="F20" t="s">
+        <v>44</v>
+      </c>
+      <c r="G20" t="s">
+        <v>44</v>
+      </c>
+    </row>
+    <row r="21" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A21">
+        <v>20</v>
+      </c>
+      <c r="B21" t="s">
+        <v>143</v>
+      </c>
+      <c r="C21" t="s">
+        <v>159</v>
+      </c>
+      <c r="D21" t="s">
+        <v>74</v>
+      </c>
+      <c r="E21" t="s">
+        <v>75</v>
+      </c>
+      <c r="F21" t="s">
+        <v>44</v>
+      </c>
+      <c r="G21" t="s">
+        <v>44</v>
+      </c>
+    </row>
+    <row r="22" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A22">
+        <v>21</v>
+      </c>
+      <c r="B22" t="s">
+        <v>143</v>
+      </c>
+      <c r="C22" t="s">
+        <v>76</v>
+      </c>
+      <c r="D22" t="s">
+        <v>77</v>
+      </c>
+      <c r="E22" t="s">
+        <v>78</v>
+      </c>
+      <c r="F22" t="s">
+        <v>44</v>
+      </c>
+      <c r="G22" t="s">
+        <v>44</v>
+      </c>
+    </row>
+    <row r="23" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A23">
+        <v>22</v>
+      </c>
+      <c r="B23" t="s">
+        <v>143</v>
+      </c>
+      <c r="C23" t="s">
+        <v>79</v>
+      </c>
+      <c r="D23" t="s">
+        <v>80</v>
+      </c>
+      <c r="E23" t="s">
+        <v>81</v>
+      </c>
+      <c r="F23" t="s">
+        <v>44</v>
+      </c>
+      <c r="G23" t="s">
+        <v>44</v>
+      </c>
+    </row>
+    <row r="24" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A24">
+        <v>23</v>
+      </c>
+      <c r="B24" t="s">
+        <v>143</v>
+      </c>
+      <c r="C24" t="s">
+        <v>144</v>
+      </c>
+      <c r="D24" s="1" t="s">
+        <v>82</v>
+      </c>
+      <c r="E24" s="1" t="s">
+        <v>82</v>
+      </c>
+      <c r="F24" s="1" t="s">
+        <v>82</v>
+      </c>
+      <c r="G24" s="1" t="s">
+        <v>82</v>
+      </c>
+    </row>
+    <row r="25" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A25">
+        <v>24</v>
+      </c>
+      <c r="B25" t="s">
+        <v>143</v>
+      </c>
+      <c r="C25" t="s">
+        <v>158</v>
+      </c>
+      <c r="D25" t="s">
+        <v>83</v>
+      </c>
+      <c r="E25" t="s">
+        <v>84</v>
+      </c>
+      <c r="F25" t="s">
+        <v>85</v>
+      </c>
+      <c r="G25" t="s">
+        <v>86</v>
+      </c>
+    </row>
+    <row r="26" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A26">
+        <v>25</v>
+      </c>
+      <c r="B26" t="s">
+        <v>143</v>
+      </c>
+      <c r="C26" t="s">
+        <v>145</v>
+      </c>
+      <c r="D26" t="s">
+        <v>87</v>
+      </c>
+      <c r="E26" t="s">
+        <v>88</v>
+      </c>
+      <c r="F26" t="s">
+        <v>89</v>
+      </c>
+      <c r="G26" t="s">
+        <v>90</v>
+      </c>
+    </row>
+    <row r="27" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A27">
+        <v>26</v>
+      </c>
+      <c r="B27" t="s">
+        <v>143</v>
+      </c>
+      <c r="C27" t="s">
+        <v>146</v>
+      </c>
+      <c r="D27" t="s">
+        <v>91</v>
+      </c>
+      <c r="E27" t="s">
+        <v>92</v>
+      </c>
+      <c r="F27" t="s">
+        <v>93</v>
+      </c>
+      <c r="G27" t="s">
+        <v>94</v>
+      </c>
+    </row>
+    <row r="28" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A28">
+        <v>27</v>
+      </c>
+      <c r="B28" t="s">
+        <v>143</v>
+      </c>
+      <c r="C28" t="s">
+        <v>147</v>
+      </c>
+      <c r="D28" t="s">
+        <v>95</v>
+      </c>
+      <c r="E28" t="s">
+        <v>96</v>
+      </c>
+      <c r="F28" t="s">
+        <v>97</v>
+      </c>
+      <c r="G28" t="s">
+        <v>98</v>
+      </c>
+    </row>
+    <row r="29" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A29">
+        <v>28</v>
+      </c>
+      <c r="B29" t="s">
+        <v>143</v>
+      </c>
+      <c r="C29" t="s">
+        <v>148</v>
+      </c>
+      <c r="D29" t="s">
+        <v>99</v>
+      </c>
+      <c r="E29" t="s">
+        <v>100</v>
+      </c>
+      <c r="F29" t="s">
+        <v>82</v>
+      </c>
+      <c r="G29" t="s">
+        <v>82</v>
+      </c>
+    </row>
+    <row r="30" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A30">
+        <v>29</v>
+      </c>
+      <c r="B30" t="s">
+        <v>143</v>
+      </c>
+      <c r="C30" t="s">
+        <v>149</v>
+      </c>
+      <c r="D30" t="s">
+        <v>101</v>
+      </c>
+      <c r="E30" t="s">
+        <v>102</v>
+      </c>
+      <c r="F30" t="s">
+        <v>103</v>
+      </c>
+      <c r="G30" t="s">
+        <v>104</v>
+      </c>
+    </row>
+    <row r="31" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A31">
+        <v>30</v>
+      </c>
+      <c r="B31" t="s">
+        <v>143</v>
+      </c>
+      <c r="C31" t="s">
+        <v>150</v>
+      </c>
+      <c r="D31" t="s">
+        <v>105</v>
+      </c>
+      <c r="E31" t="s">
+        <v>106</v>
+      </c>
+      <c r="F31" t="s">
+        <v>82</v>
+      </c>
+      <c r="G31" t="s">
+        <v>82</v>
+      </c>
+    </row>
+    <row r="32" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A32">
+        <v>31</v>
+      </c>
+      <c r="B32" t="s">
+        <v>143</v>
+      </c>
+      <c r="C32" t="s">
+        <v>151</v>
+      </c>
+      <c r="D32" t="s">
+        <v>108</v>
+      </c>
+      <c r="E32" t="s">
+        <v>109</v>
+      </c>
+      <c r="F32" t="s">
+        <v>110</v>
+      </c>
+      <c r="G32" t="s">
+        <v>111</v>
+      </c>
+    </row>
+    <row r="33" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A33">
+        <v>32</v>
+      </c>
+      <c r="B33" t="s">
+        <v>143</v>
+      </c>
+      <c r="C33" t="s">
+        <v>152</v>
+      </c>
+      <c r="D33" t="s">
+        <v>112</v>
+      </c>
+      <c r="E33" t="s">
+        <v>113</v>
+      </c>
+      <c r="F33" t="s">
+        <v>114</v>
+      </c>
+      <c r="G33" t="s">
+        <v>115</v>
+      </c>
+    </row>
+    <row r="34" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A34">
+        <v>33</v>
+      </c>
+      <c r="B34" t="s">
+        <v>143</v>
+      </c>
+      <c r="C34" t="s">
+        <v>153</v>
+      </c>
+      <c r="D34" t="s">
+        <v>117</v>
+      </c>
+      <c r="E34" t="s">
+        <v>118</v>
+      </c>
+      <c r="F34" t="s">
+        <v>119</v>
+      </c>
+      <c r="G34" t="s">
+        <v>120</v>
+      </c>
+    </row>
+    <row r="35" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A35">
+        <v>34</v>
+      </c>
+      <c r="B35" t="s">
+        <v>143</v>
+      </c>
+      <c r="C35" t="s">
+        <v>154</v>
+      </c>
+      <c r="D35" t="s">
+        <v>121</v>
+      </c>
+      <c r="E35" t="s">
+        <v>122</v>
+      </c>
+      <c r="F35" t="s">
+        <v>123</v>
+      </c>
+      <c r="G35" t="s">
+        <v>124</v>
+      </c>
+    </row>
+    <row r="36" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A36">
+        <v>35</v>
+      </c>
+      <c r="B36" t="s">
+        <v>143</v>
+      </c>
+      <c r="C36" t="s">
+        <v>155</v>
+      </c>
+      <c r="D36" t="s">
+        <v>125</v>
+      </c>
+      <c r="E36" t="s">
+        <v>126</v>
+      </c>
+      <c r="F36" t="s">
+        <v>127</v>
+      </c>
+      <c r="G36" t="s">
+        <v>128</v>
+      </c>
+    </row>
+    <row r="37" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A37">
+        <v>36</v>
+      </c>
+      <c r="B37" t="s">
+        <v>143</v>
+      </c>
+      <c r="C37" t="s">
+        <v>156</v>
+      </c>
+      <c r="D37" t="s">
+        <v>129</v>
+      </c>
+      <c r="E37" t="s">
+        <v>130</v>
+      </c>
+      <c r="F37" t="s">
+        <v>131</v>
+      </c>
+      <c r="G37" t="s">
+        <v>132</v>
+      </c>
+    </row>
+    <row r="38" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A38">
+        <v>37</v>
+      </c>
+      <c r="B38" t="s">
+        <v>143</v>
+      </c>
+      <c r="C38" t="s">
+        <v>157</v>
+      </c>
+      <c r="D38" t="s">
+        <v>133</v>
+      </c>
+      <c r="E38" t="s">
+        <v>134</v>
+      </c>
+      <c r="F38" t="s">
+        <v>135</v>
+      </c>
+      <c r="G38" t="s">
+        <v>136</v>
+      </c>
+    </row>
+    <row r="39" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A39">
+        <v>38</v>
+      </c>
+      <c r="B39" t="s">
+        <v>143</v>
+      </c>
+      <c r="C39" t="s">
+        <v>137</v>
+      </c>
+      <c r="D39" t="s">
+        <v>138</v>
+      </c>
+      <c r="E39" t="s">
+        <v>139</v>
+      </c>
+      <c r="F39" t="s">
+        <v>140</v>
+      </c>
+      <c r="G39" t="s">
+        <v>141</v>
       </c>
     </row>
   </sheetData>

--- a/2- BB.DD. SERVICIOS Y UNIDADES/BBDD SERVICIOS Y UNIDADES.xlsx
+++ b/2- BB.DD. SERVICIOS Y UNIDADES/BBDD SERVICIOS Y UNIDADES.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\IPLACEX\Año 2\PRÁCTICA IPLACEX\PLATAFORMA PASANTÍAS\GITHUB\2- BB.DD. SERVICIOS Y UNIDADES\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{906C785C-3FFB-4E84-98D4-6C6496983217}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{8BD0C93C-BE60-42FA-A401-1CC497734224}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-28920" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{7936E908-9EDA-4102-87A8-C4382552261F}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{7936E908-9EDA-4102-87A8-C4382552261F}"/>
   </bookViews>
   <sheets>
     <sheet name="Hoja1" sheetId="1" r:id="rId1"/>
@@ -39,7 +39,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="236" uniqueCount="172">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="536" uniqueCount="330">
   <si>
     <t>id</t>
   </si>
@@ -555,6 +555,480 @@
   </si>
   <si>
     <t>servicio/unidad/cr</t>
+  </si>
+  <si>
+    <t>administrativa</t>
+  </si>
+  <si>
+    <t>recursos físicos</t>
+  </si>
+  <si>
+    <t>jorge karmi román</t>
+  </si>
+  <si>
+    <t>jorge.karmi@redsalud.gob.cl</t>
+  </si>
+  <si>
+    <t>stanka cvjetkovic</t>
+  </si>
+  <si>
+    <t>stanka.ninoska@redsalud.gob.cl</t>
+  </si>
+  <si>
+    <t>finanzas</t>
+  </si>
+  <si>
+    <t>susana veloso azócar</t>
+  </si>
+  <si>
+    <t>susana.veloso@redsalud.gob.cl</t>
+  </si>
+  <si>
+    <t>joel becerra</t>
+  </si>
+  <si>
+    <t>joel.becerra@redsalud.gob.cl</t>
+  </si>
+  <si>
+    <t>abastecimiento</t>
+  </si>
+  <si>
+    <t>rodrigo bravo gajardo</t>
+  </si>
+  <si>
+    <t>rodrigo.bravog@redsalud.gob.cl</t>
+  </si>
+  <si>
+    <t>richard faundez</t>
+  </si>
+  <si>
+    <t>richard.faundez@redsalud.gob.cl</t>
+  </si>
+  <si>
+    <t>archivo</t>
+  </si>
+  <si>
+    <t>evelyn lobos salazar</t>
+  </si>
+  <si>
+    <t>evelyn.lobos.s@redsalud.gob.cl</t>
+  </si>
+  <si>
+    <t>alejandra padilla</t>
+  </si>
+  <si>
+    <t>carolina pizarro</t>
+  </si>
+  <si>
+    <t>carolina.pizarro.j@redsalud.gob.cl</t>
+  </si>
+  <si>
+    <t>scarlett yevilao riquelme</t>
+  </si>
+  <si>
+    <t>scarlett.yevilao@redsalud.gob.cl</t>
+  </si>
+  <si>
+    <t>gestión de los cuidados de enfermería</t>
+  </si>
+  <si>
+    <t>cuidados urgencia</t>
+  </si>
+  <si>
+    <t>liliana vega espinoza</t>
+  </si>
+  <si>
+    <t>cuidados de paciente en estado transitorio</t>
+  </si>
+  <si>
+    <t>pamela uribe díaz</t>
+  </si>
+  <si>
+    <t>cuidados de atención ambulatoria</t>
+  </si>
+  <si>
+    <t>carolina fernández lagos</t>
+  </si>
+  <si>
+    <t>carolina.fernandez@redsalud.gob.cl</t>
+  </si>
+  <si>
+    <t>cuidados médicos</t>
+  </si>
+  <si>
+    <t>sandra selanio araya</t>
+  </si>
+  <si>
+    <t>cuidados agudos</t>
+  </si>
+  <si>
+    <t>jeanette lillo</t>
+  </si>
+  <si>
+    <t>complejo chacabuco (uga - mq chacabuco)</t>
+  </si>
+  <si>
+    <t>daniela rivera candia</t>
+  </si>
+  <si>
+    <t>cuidados diabetes hospitalizado</t>
+  </si>
+  <si>
+    <t>camila vásquez alegre</t>
+  </si>
+  <si>
+    <t>camila.vasquez.a@redsalud.gob.cl</t>
+  </si>
+  <si>
+    <t>cuidados pabellón</t>
+  </si>
+  <si>
+    <t>maría dolores candia álvarez</t>
+  </si>
+  <si>
+    <t>cuidados de pabellón de urgencia y recuperación</t>
+  </si>
+  <si>
+    <t>romina galleguillos pearson</t>
+  </si>
+  <si>
+    <t>cuidados de pabellón central</t>
+  </si>
+  <si>
+    <t>rocío briones martínez</t>
+  </si>
+  <si>
+    <t>cuidados de pabellón cdt</t>
+  </si>
+  <si>
+    <t>jenny lobos poza</t>
+  </si>
+  <si>
+    <t>cuidados de hospitalización transitoria</t>
+  </si>
+  <si>
+    <t>simón maripangui orellana</t>
+  </si>
+  <si>
+    <t>simon.maripangui.o@redsalud.gob.cl</t>
+  </si>
+  <si>
+    <t>cuidados quirúrgicos</t>
+  </si>
+  <si>
+    <t>lidia weisse acuña</t>
+  </si>
+  <si>
+    <t>cuidados agudos quirúrgicos</t>
+  </si>
+  <si>
+    <t>lissette tejada arce</t>
+  </si>
+  <si>
+    <t>cuidados especiales quirúrgicos (mq torre)</t>
+  </si>
+  <si>
+    <t>marjorie guzman muñoz</t>
+  </si>
+  <si>
+    <t>cuidados subespecialidades qx</t>
+  </si>
+  <si>
+    <t>viviana sánchez rojas</t>
+  </si>
+  <si>
+    <t>viviana.sanchez.r@redsalud.gob.cl</t>
+  </si>
+  <si>
+    <t>cuidados neurológicos</t>
+  </si>
+  <si>
+    <t>tamara pulgar vargas</t>
+  </si>
+  <si>
+    <t>tamara.pulgar@redsalud.gob.cl</t>
+  </si>
+  <si>
+    <t>cuidados críticos adultos</t>
+  </si>
+  <si>
+    <t>karina aguirre sepúlveda</t>
+  </si>
+  <si>
+    <t>unidad de cuidados intensivos críticos</t>
+  </si>
+  <si>
+    <t>daniela rebolledo oyarzo</t>
+  </si>
+  <si>
+    <t>daniela.rebolledo@redsalud.gob.cl</t>
+  </si>
+  <si>
+    <t>unidad cuidados intensivos quirúrgicos</t>
+  </si>
+  <si>
+    <t>camila rojas méndez</t>
+  </si>
+  <si>
+    <t>camila.rojas.m@redsalud.gob.cl</t>
+  </si>
+  <si>
+    <t>unidad intensivo médico</t>
+  </si>
+  <si>
+    <t>lizbeth fuentealba vásquez</t>
+  </si>
+  <si>
+    <t>cuidados infantiles</t>
+  </si>
+  <si>
+    <t>ana arriagada obregón</t>
+  </si>
+  <si>
+    <t>cuidados hematooncológicos infantiles</t>
+  </si>
+  <si>
+    <t>bernardita ubilla rojas</t>
+  </si>
+  <si>
+    <t>bernardita.ubilla@redsalud.gob.cl</t>
+  </si>
+  <si>
+    <t>cuidados médicos quirúrgico infantil</t>
+  </si>
+  <si>
+    <t>eva becerra valladares</t>
+  </si>
+  <si>
+    <t>cuidados paciente crítico pediátrico</t>
+  </si>
+  <si>
+    <t>marcela aguirre meléndez</t>
+  </si>
+  <si>
+    <t>marcela.aguirrem@redsalud.gob.cl</t>
+  </si>
+  <si>
+    <t>cuidados ambulatorios</t>
+  </si>
+  <si>
+    <t>catherine larenas bilbao</t>
+  </si>
+  <si>
+    <t>cuidados consultas adulto</t>
+  </si>
+  <si>
+    <t>ruth gutiérrez zamorano</t>
+  </si>
+  <si>
+    <t>ruth.gutierrez@redsalud.gob.cl</t>
+  </si>
+  <si>
+    <t>cuidados procedimientos endoscópicos</t>
+  </si>
+  <si>
+    <t>catherine navarrete barril</t>
+  </si>
+  <si>
+    <t>cuidados nefrológicos</t>
+  </si>
+  <si>
+    <t>paula guerra herrera</t>
+  </si>
+  <si>
+    <t>cuidados consultas pediátrica</t>
+  </si>
+  <si>
+    <t>daniela toledo salas</t>
+  </si>
+  <si>
+    <t>daniela.toledo@redsalud.gob.cl</t>
+  </si>
+  <si>
+    <t>cuidados hemato-oncológicos</t>
+  </si>
+  <si>
+    <t>susan bravo cifuentes</t>
+  </si>
+  <si>
+    <t>cuidados hematooncológico adulto</t>
+  </si>
+  <si>
+    <t>lisset santibáñez rojas</t>
+  </si>
+  <si>
+    <t>lisset.santibanez@redsalud.gob.cl</t>
+  </si>
+  <si>
+    <t>quimioterapia ambulatoria infantil</t>
+  </si>
+  <si>
+    <t>camila urrea meza</t>
+  </si>
+  <si>
+    <t>camila.urrea@redsalud.gob.cl</t>
+  </si>
+  <si>
+    <t>quimioterapia ambulatoria adulta</t>
+  </si>
+  <si>
+    <t>carolina ruz barahona</t>
+  </si>
+  <si>
+    <t>cuidados paliativos y alivio del dolor</t>
+  </si>
+  <si>
+    <t>josé molina alavarez</t>
+  </si>
+  <si>
+    <t>cuidados hematooncológico hospitalizado</t>
+  </si>
+  <si>
+    <t>evelyn salinas matalon</t>
+  </si>
+  <si>
+    <t>evelyn.salinas@redsalud.gob.cl</t>
+  </si>
+  <si>
+    <t>coordinación hematooncológica</t>
+  </si>
+  <si>
+    <t>cuidados hospitalización domiciliaria</t>
+  </si>
+  <si>
+    <t>mackarenna saez fuentes</t>
+  </si>
+  <si>
+    <t>cuidados hospitalización domiciliaria adulto</t>
+  </si>
+  <si>
+    <t>nickoll iraola díaz</t>
+  </si>
+  <si>
+    <t>nickoll.iraola@redsalud.gob.cl</t>
+  </si>
+  <si>
+    <t>cuidados hospitalización domiciliaria infantil</t>
+  </si>
+  <si>
+    <t>doris vargas álvarez</t>
+  </si>
+  <si>
+    <t>doris.vargas@redsalud.gob.cl</t>
+  </si>
+  <si>
+    <t>esterilización</t>
+  </si>
+  <si>
+    <t>cynthya ramos leiva</t>
+  </si>
+  <si>
+    <t>cynthya.ramos@redsalud.gob.cl</t>
+  </si>
+  <si>
+    <t>cuidados cardiovascular</t>
+  </si>
+  <si>
+    <t>shirley rustom</t>
+  </si>
+  <si>
+    <t>cuidados intensivos coronarios</t>
+  </si>
+  <si>
+    <t>lucía toro quijada</t>
+  </si>
+  <si>
+    <t>lucia.toro@redsalud.gob.cl</t>
+  </si>
+  <si>
+    <t>cardiología intervencional</t>
+  </si>
+  <si>
+    <t>angélica galleguillos zamora</t>
+  </si>
+  <si>
+    <t>angelicagalleguillos@redsalud.gob.cl</t>
+  </si>
+  <si>
+    <t>cuidados de cardiocirugía</t>
+  </si>
+  <si>
+    <t>valentina jara toro</t>
+  </si>
+  <si>
+    <t>valentina.jara@redsalud.gob.cl</t>
+  </si>
+  <si>
+    <t>cuidados policlínico cardiológico</t>
+  </si>
+  <si>
+    <t>daniela fuenzalida andrade</t>
+  </si>
+  <si>
+    <t>daniela.fuenzalida@redsalud.gob.cl</t>
+  </si>
+  <si>
+    <t>liliana.vegae@redsalud.gob.cl</t>
+  </si>
+  <si>
+    <t>pamela.uribe@redsalud.gob.cl</t>
+  </si>
+  <si>
+    <t>sandra.selanio@redsalud.gob.cl</t>
+  </si>
+  <si>
+    <t>daniela.riverac@redsalud.gob.cl</t>
+  </si>
+  <si>
+    <t>maria.candia@redsalud.gob.cl</t>
+  </si>
+  <si>
+    <t>romina.galleguillos@redsalud.gob.cl</t>
+  </si>
+  <si>
+    <t>rocio.brionesm@redsalud.gob.cl</t>
+  </si>
+  <si>
+    <t>jenny.lobos@redsalud.gob.cl</t>
+  </si>
+  <si>
+    <t>lidia.weisse@redsalud.gob.cl</t>
+  </si>
+  <si>
+    <t>lissette.tejada@redsalud.gob.cl</t>
+  </si>
+  <si>
+    <t>marjorie.guzman@redsalud.gob.cl</t>
+  </si>
+  <si>
+    <t>karina.aguirre@redsalud.gob.cl</t>
+  </si>
+  <si>
+    <t>lizbeth.fuentealba@redsalud.gob.cl</t>
+  </si>
+  <si>
+    <t>ana.arriagada@redsalud.gob.cl</t>
+  </si>
+  <si>
+    <t>eva.becerra@redsalud.gob.cl</t>
+  </si>
+  <si>
+    <t>catherine.larenas@redsalud.gob.cl</t>
+  </si>
+  <si>
+    <t>catherine.navarrete@redsalud.gob.cl</t>
+  </si>
+  <si>
+    <t>paula.guerra@redsalud.gob.cl</t>
+  </si>
+  <si>
+    <t>susan.bravo@redsalud.gob.cl</t>
+  </si>
+  <si>
+    <t>mackarenna.saez@redsalud.gob.cl</t>
+  </si>
+  <si>
+    <t>shirley.rustom@redsalud.gob.cl</t>
   </si>
 </sst>
 </file>
@@ -933,11 +1407,16 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{37800E50-6288-4855-903E-7D1C9ED078D0}">
-  <dimension ref="A1:H39"/>
+  <dimension ref="A1:H89"/>
   <sheetFormatPr baseColWidth="10" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="3" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="34.140625" customWidth="1"/>
+    <col min="2" max="2" width="35" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="45.140625" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="33.140625" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="40" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="32.7109375" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="34" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:8" x14ac:dyDescent="0.25">
@@ -1482,17 +1961,17 @@
       <c r="C24" t="s">
         <v>144</v>
       </c>
-      <c r="D24" s="1" t="s">
-        <v>82</v>
-      </c>
-      <c r="E24" s="1" t="s">
-        <v>82</v>
-      </c>
-      <c r="F24" s="1" t="s">
-        <v>82</v>
-      </c>
-      <c r="G24" s="1" t="s">
-        <v>82</v>
+      <c r="D24" t="s">
+        <v>192</v>
+      </c>
+      <c r="E24" t="s">
+        <v>193</v>
+      </c>
+      <c r="F24" t="s">
+        <v>194</v>
+      </c>
+      <c r="G24" t="s">
+        <v>195</v>
       </c>
     </row>
     <row r="25" spans="1:7" x14ac:dyDescent="0.25">
@@ -1603,10 +2082,10 @@
       <c r="E29" t="s">
         <v>100</v>
       </c>
-      <c r="F29" t="s">
-        <v>82</v>
-      </c>
-      <c r="G29" t="s">
+      <c r="F29" s="1" t="s">
+        <v>82</v>
+      </c>
+      <c r="G29" s="1" t="s">
         <v>82</v>
       </c>
     </row>
@@ -1649,10 +2128,10 @@
       <c r="E31" t="s">
         <v>106</v>
       </c>
-      <c r="F31" t="s">
-        <v>82</v>
-      </c>
-      <c r="G31" t="s">
+      <c r="F31" s="1" t="s">
+        <v>82</v>
+      </c>
+      <c r="G31" s="1" t="s">
         <v>82</v>
       </c>
     </row>
@@ -1838,6 +2317,1156 @@
       </c>
       <c r="G39" t="s">
         <v>141</v>
+      </c>
+    </row>
+    <row r="40" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A40">
+        <v>39</v>
+      </c>
+      <c r="B40" t="s">
+        <v>172</v>
+      </c>
+      <c r="C40" t="s">
+        <v>173</v>
+      </c>
+      <c r="D40" t="s">
+        <v>174</v>
+      </c>
+      <c r="E40" t="s">
+        <v>175</v>
+      </c>
+      <c r="F40" t="s">
+        <v>176</v>
+      </c>
+      <c r="G40" t="s">
+        <v>177</v>
+      </c>
+    </row>
+    <row r="41" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A41">
+        <v>40</v>
+      </c>
+      <c r="B41" t="s">
+        <v>172</v>
+      </c>
+      <c r="C41" t="s">
+        <v>178</v>
+      </c>
+      <c r="D41" t="s">
+        <v>179</v>
+      </c>
+      <c r="E41" t="s">
+        <v>180</v>
+      </c>
+      <c r="F41" t="s">
+        <v>181</v>
+      </c>
+      <c r="G41" t="s">
+        <v>182</v>
+      </c>
+    </row>
+    <row r="42" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A42">
+        <v>41</v>
+      </c>
+      <c r="B42" t="s">
+        <v>172</v>
+      </c>
+      <c r="C42" t="s">
+        <v>183</v>
+      </c>
+      <c r="D42" t="s">
+        <v>184</v>
+      </c>
+      <c r="E42" t="s">
+        <v>185</v>
+      </c>
+      <c r="F42" t="s">
+        <v>186</v>
+      </c>
+      <c r="G42" t="s">
+        <v>187</v>
+      </c>
+    </row>
+    <row r="43" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A43">
+        <v>42</v>
+      </c>
+      <c r="B43" t="s">
+        <v>172</v>
+      </c>
+      <c r="C43" t="s">
+        <v>188</v>
+      </c>
+      <c r="D43" t="s">
+        <v>189</v>
+      </c>
+      <c r="E43" t="s">
+        <v>190</v>
+      </c>
+      <c r="F43" t="s">
+        <v>191</v>
+      </c>
+      <c r="G43" s="1" t="s">
+        <v>82</v>
+      </c>
+    </row>
+    <row r="44" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A44">
+        <v>43</v>
+      </c>
+      <c r="B44" t="s">
+        <v>196</v>
+      </c>
+      <c r="C44" t="s">
+        <v>197</v>
+      </c>
+      <c r="D44" t="s">
+        <v>198</v>
+      </c>
+      <c r="E44" t="s">
+        <v>309</v>
+      </c>
+      <c r="F44" s="1" t="s">
+        <v>82</v>
+      </c>
+      <c r="G44" s="1" t="s">
+        <v>82</v>
+      </c>
+    </row>
+    <row r="45" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A45">
+        <v>44</v>
+      </c>
+      <c r="B45" t="s">
+        <v>196</v>
+      </c>
+      <c r="C45" t="s">
+        <v>199</v>
+      </c>
+      <c r="D45" t="s">
+        <v>200</v>
+      </c>
+      <c r="E45" t="s">
+        <v>310</v>
+      </c>
+      <c r="F45" s="1" t="s">
+        <v>82</v>
+      </c>
+      <c r="G45" s="1" t="s">
+        <v>82</v>
+      </c>
+    </row>
+    <row r="46" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A46">
+        <v>45</v>
+      </c>
+      <c r="B46" t="s">
+        <v>196</v>
+      </c>
+      <c r="C46" t="s">
+        <v>201</v>
+      </c>
+      <c r="D46" t="s">
+        <v>202</v>
+      </c>
+      <c r="E46" t="s">
+        <v>203</v>
+      </c>
+      <c r="F46" s="1" t="s">
+        <v>82</v>
+      </c>
+      <c r="G46" s="1" t="s">
+        <v>82</v>
+      </c>
+    </row>
+    <row r="47" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A47">
+        <v>46</v>
+      </c>
+      <c r="B47" t="s">
+        <v>196</v>
+      </c>
+      <c r="C47" t="s">
+        <v>204</v>
+      </c>
+      <c r="D47" t="s">
+        <v>205</v>
+      </c>
+      <c r="E47" t="s">
+        <v>311</v>
+      </c>
+      <c r="F47" s="1" t="s">
+        <v>82</v>
+      </c>
+      <c r="G47" s="1" t="s">
+        <v>82</v>
+      </c>
+    </row>
+    <row r="48" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A48">
+        <v>47</v>
+      </c>
+      <c r="B48" t="s">
+        <v>196</v>
+      </c>
+      <c r="C48" t="s">
+        <v>206</v>
+      </c>
+      <c r="D48" t="s">
+        <v>207</v>
+      </c>
+      <c r="E48" s="1" t="s">
+        <v>82</v>
+      </c>
+      <c r="F48" s="1" t="s">
+        <v>82</v>
+      </c>
+      <c r="G48" s="1" t="s">
+        <v>82</v>
+      </c>
+    </row>
+    <row r="49" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A49">
+        <v>48</v>
+      </c>
+      <c r="B49" t="s">
+        <v>196</v>
+      </c>
+      <c r="C49" t="s">
+        <v>208</v>
+      </c>
+      <c r="D49" t="s">
+        <v>209</v>
+      </c>
+      <c r="E49" t="s">
+        <v>312</v>
+      </c>
+      <c r="F49" s="1" t="s">
+        <v>82</v>
+      </c>
+      <c r="G49" s="1" t="s">
+        <v>82</v>
+      </c>
+    </row>
+    <row r="50" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A50">
+        <v>49</v>
+      </c>
+      <c r="B50" t="s">
+        <v>196</v>
+      </c>
+      <c r="C50" t="s">
+        <v>210</v>
+      </c>
+      <c r="D50" t="s">
+        <v>211</v>
+      </c>
+      <c r="E50" t="s">
+        <v>212</v>
+      </c>
+      <c r="F50" s="1" t="s">
+        <v>82</v>
+      </c>
+      <c r="G50" s="1" t="s">
+        <v>82</v>
+      </c>
+    </row>
+    <row r="51" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A51">
+        <v>50</v>
+      </c>
+      <c r="B51" t="s">
+        <v>196</v>
+      </c>
+      <c r="C51" t="s">
+        <v>213</v>
+      </c>
+      <c r="D51" t="s">
+        <v>214</v>
+      </c>
+      <c r="E51" t="s">
+        <v>313</v>
+      </c>
+      <c r="F51" s="1" t="s">
+        <v>82</v>
+      </c>
+      <c r="G51" s="1" t="s">
+        <v>82</v>
+      </c>
+    </row>
+    <row r="52" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A52">
+        <v>51</v>
+      </c>
+      <c r="B52" t="s">
+        <v>196</v>
+      </c>
+      <c r="C52" t="s">
+        <v>215</v>
+      </c>
+      <c r="D52" t="s">
+        <v>216</v>
+      </c>
+      <c r="E52" t="s">
+        <v>314</v>
+      </c>
+      <c r="F52" s="1" t="s">
+        <v>82</v>
+      </c>
+      <c r="G52" s="1" t="s">
+        <v>82</v>
+      </c>
+    </row>
+    <row r="53" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A53">
+        <v>52</v>
+      </c>
+      <c r="B53" t="s">
+        <v>196</v>
+      </c>
+      <c r="C53" t="s">
+        <v>217</v>
+      </c>
+      <c r="D53" t="s">
+        <v>218</v>
+      </c>
+      <c r="E53" t="s">
+        <v>315</v>
+      </c>
+      <c r="F53" s="1" t="s">
+        <v>82</v>
+      </c>
+      <c r="G53" s="1" t="s">
+        <v>82</v>
+      </c>
+    </row>
+    <row r="54" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A54">
+        <v>53</v>
+      </c>
+      <c r="B54" t="s">
+        <v>196</v>
+      </c>
+      <c r="C54" t="s">
+        <v>219</v>
+      </c>
+      <c r="D54" t="s">
+        <v>220</v>
+      </c>
+      <c r="E54" t="s">
+        <v>316</v>
+      </c>
+      <c r="F54" s="1" t="s">
+        <v>82</v>
+      </c>
+      <c r="G54" s="1" t="s">
+        <v>82</v>
+      </c>
+    </row>
+    <row r="55" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A55">
+        <v>54</v>
+      </c>
+      <c r="B55" t="s">
+        <v>196</v>
+      </c>
+      <c r="C55" t="s">
+        <v>221</v>
+      </c>
+      <c r="D55" t="s">
+        <v>222</v>
+      </c>
+      <c r="E55" t="s">
+        <v>223</v>
+      </c>
+      <c r="F55" s="1" t="s">
+        <v>82</v>
+      </c>
+      <c r="G55" s="1" t="s">
+        <v>82</v>
+      </c>
+    </row>
+    <row r="56" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A56">
+        <v>55</v>
+      </c>
+      <c r="B56" t="s">
+        <v>196</v>
+      </c>
+      <c r="C56" t="s">
+        <v>224</v>
+      </c>
+      <c r="D56" t="s">
+        <v>225</v>
+      </c>
+      <c r="E56" t="s">
+        <v>317</v>
+      </c>
+      <c r="F56" s="1" t="s">
+        <v>82</v>
+      </c>
+      <c r="G56" s="1" t="s">
+        <v>82</v>
+      </c>
+    </row>
+    <row r="57" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A57">
+        <v>56</v>
+      </c>
+      <c r="B57" t="s">
+        <v>196</v>
+      </c>
+      <c r="C57" t="s">
+        <v>226</v>
+      </c>
+      <c r="D57" t="s">
+        <v>227</v>
+      </c>
+      <c r="E57" t="s">
+        <v>318</v>
+      </c>
+      <c r="F57" s="1" t="s">
+        <v>82</v>
+      </c>
+      <c r="G57" s="1" t="s">
+        <v>82</v>
+      </c>
+    </row>
+    <row r="58" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A58">
+        <v>57</v>
+      </c>
+      <c r="B58" t="s">
+        <v>196</v>
+      </c>
+      <c r="C58" t="s">
+        <v>228</v>
+      </c>
+      <c r="D58" t="s">
+        <v>229</v>
+      </c>
+      <c r="E58" t="s">
+        <v>319</v>
+      </c>
+      <c r="F58" s="1" t="s">
+        <v>82</v>
+      </c>
+      <c r="G58" s="1" t="s">
+        <v>82</v>
+      </c>
+    </row>
+    <row r="59" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A59">
+        <v>58</v>
+      </c>
+      <c r="B59" t="s">
+        <v>196</v>
+      </c>
+      <c r="C59" t="s">
+        <v>230</v>
+      </c>
+      <c r="D59" t="s">
+        <v>231</v>
+      </c>
+      <c r="E59" t="s">
+        <v>232</v>
+      </c>
+      <c r="F59" s="1" t="s">
+        <v>82</v>
+      </c>
+      <c r="G59" s="1" t="s">
+        <v>82</v>
+      </c>
+    </row>
+    <row r="60" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A60">
+        <v>59</v>
+      </c>
+      <c r="B60" t="s">
+        <v>196</v>
+      </c>
+      <c r="C60" t="s">
+        <v>233</v>
+      </c>
+      <c r="D60" t="s">
+        <v>234</v>
+      </c>
+      <c r="E60" t="s">
+        <v>235</v>
+      </c>
+      <c r="F60" s="1" t="s">
+        <v>82</v>
+      </c>
+      <c r="G60" s="1" t="s">
+        <v>82</v>
+      </c>
+    </row>
+    <row r="61" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A61">
+        <v>60</v>
+      </c>
+      <c r="B61" t="s">
+        <v>196</v>
+      </c>
+      <c r="C61" t="s">
+        <v>236</v>
+      </c>
+      <c r="D61" t="s">
+        <v>237</v>
+      </c>
+      <c r="E61" t="s">
+        <v>320</v>
+      </c>
+      <c r="F61" s="1" t="s">
+        <v>82</v>
+      </c>
+      <c r="G61" s="1" t="s">
+        <v>82</v>
+      </c>
+    </row>
+    <row r="62" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A62">
+        <v>61</v>
+      </c>
+      <c r="B62" t="s">
+        <v>196</v>
+      </c>
+      <c r="C62" t="s">
+        <v>238</v>
+      </c>
+      <c r="D62" t="s">
+        <v>239</v>
+      </c>
+      <c r="E62" t="s">
+        <v>240</v>
+      </c>
+      <c r="F62" s="1" t="s">
+        <v>82</v>
+      </c>
+      <c r="G62" s="1" t="s">
+        <v>82</v>
+      </c>
+    </row>
+    <row r="63" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A63">
+        <v>62</v>
+      </c>
+      <c r="B63" t="s">
+        <v>196</v>
+      </c>
+      <c r="C63" t="s">
+        <v>241</v>
+      </c>
+      <c r="D63" t="s">
+        <v>242</v>
+      </c>
+      <c r="E63" t="s">
+        <v>243</v>
+      </c>
+      <c r="F63" s="1" t="s">
+        <v>82</v>
+      </c>
+      <c r="G63" s="1" t="s">
+        <v>82</v>
+      </c>
+    </row>
+    <row r="64" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A64">
+        <v>63</v>
+      </c>
+      <c r="B64" t="s">
+        <v>196</v>
+      </c>
+      <c r="C64" t="s">
+        <v>244</v>
+      </c>
+      <c r="D64" t="s">
+        <v>245</v>
+      </c>
+      <c r="E64" t="s">
+        <v>321</v>
+      </c>
+      <c r="F64" s="1" t="s">
+        <v>82</v>
+      </c>
+      <c r="G64" s="1" t="s">
+        <v>82</v>
+      </c>
+    </row>
+    <row r="65" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A65">
+        <v>64</v>
+      </c>
+      <c r="B65" t="s">
+        <v>196</v>
+      </c>
+      <c r="C65" t="s">
+        <v>246</v>
+      </c>
+      <c r="D65" t="s">
+        <v>247</v>
+      </c>
+      <c r="E65" t="s">
+        <v>322</v>
+      </c>
+      <c r="F65" s="1" t="s">
+        <v>82</v>
+      </c>
+      <c r="G65" s="1" t="s">
+        <v>82</v>
+      </c>
+    </row>
+    <row r="66" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A66">
+        <v>65</v>
+      </c>
+      <c r="B66" t="s">
+        <v>196</v>
+      </c>
+      <c r="C66" t="s">
+        <v>248</v>
+      </c>
+      <c r="D66" t="s">
+        <v>249</v>
+      </c>
+      <c r="E66" t="s">
+        <v>250</v>
+      </c>
+      <c r="F66" s="1" t="s">
+        <v>82</v>
+      </c>
+      <c r="G66" s="1" t="s">
+        <v>82</v>
+      </c>
+    </row>
+    <row r="67" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A67">
+        <v>66</v>
+      </c>
+      <c r="B67" t="s">
+        <v>196</v>
+      </c>
+      <c r="C67" t="s">
+        <v>251</v>
+      </c>
+      <c r="D67" t="s">
+        <v>252</v>
+      </c>
+      <c r="E67" t="s">
+        <v>323</v>
+      </c>
+      <c r="F67" s="1" t="s">
+        <v>82</v>
+      </c>
+      <c r="G67" s="1" t="s">
+        <v>82</v>
+      </c>
+    </row>
+    <row r="68" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A68">
+        <v>67</v>
+      </c>
+      <c r="B68" t="s">
+        <v>196</v>
+      </c>
+      <c r="C68" t="s">
+        <v>253</v>
+      </c>
+      <c r="D68" t="s">
+        <v>254</v>
+      </c>
+      <c r="E68" t="s">
+        <v>255</v>
+      </c>
+      <c r="F68" s="1" t="s">
+        <v>82</v>
+      </c>
+      <c r="G68" s="1" t="s">
+        <v>82</v>
+      </c>
+    </row>
+    <row r="69" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A69">
+        <v>68</v>
+      </c>
+      <c r="B69" t="s">
+        <v>196</v>
+      </c>
+      <c r="C69" t="s">
+        <v>256</v>
+      </c>
+      <c r="D69" t="s">
+        <v>257</v>
+      </c>
+      <c r="E69" t="s">
+        <v>324</v>
+      </c>
+      <c r="F69" s="1" t="s">
+        <v>82</v>
+      </c>
+      <c r="G69" s="1" t="s">
+        <v>82</v>
+      </c>
+    </row>
+    <row r="70" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A70">
+        <v>69</v>
+      </c>
+      <c r="B70" t="s">
+        <v>196</v>
+      </c>
+      <c r="C70" t="s">
+        <v>258</v>
+      </c>
+      <c r="D70" t="s">
+        <v>259</v>
+      </c>
+      <c r="E70" t="s">
+        <v>260</v>
+      </c>
+      <c r="F70" s="1" t="s">
+        <v>82</v>
+      </c>
+      <c r="G70" s="1" t="s">
+        <v>82</v>
+      </c>
+    </row>
+    <row r="71" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A71">
+        <v>70</v>
+      </c>
+      <c r="B71" t="s">
+        <v>196</v>
+      </c>
+      <c r="C71" t="s">
+        <v>261</v>
+      </c>
+      <c r="D71" t="s">
+        <v>262</v>
+      </c>
+      <c r="E71" t="s">
+        <v>325</v>
+      </c>
+      <c r="F71" s="1" t="s">
+        <v>82</v>
+      </c>
+      <c r="G71" s="1" t="s">
+        <v>82</v>
+      </c>
+    </row>
+    <row r="72" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A72">
+        <v>71</v>
+      </c>
+      <c r="B72" t="s">
+        <v>196</v>
+      </c>
+      <c r="C72" t="s">
+        <v>263</v>
+      </c>
+      <c r="D72" t="s">
+        <v>264</v>
+      </c>
+      <c r="E72" t="s">
+        <v>326</v>
+      </c>
+      <c r="F72" s="1" t="s">
+        <v>82</v>
+      </c>
+      <c r="G72" s="1" t="s">
+        <v>82</v>
+      </c>
+    </row>
+    <row r="73" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A73">
+        <v>72</v>
+      </c>
+      <c r="B73" t="s">
+        <v>196</v>
+      </c>
+      <c r="C73" t="s">
+        <v>265</v>
+      </c>
+      <c r="D73" t="s">
+        <v>266</v>
+      </c>
+      <c r="E73" t="s">
+        <v>267</v>
+      </c>
+      <c r="F73" s="1" t="s">
+        <v>82</v>
+      </c>
+      <c r="G73" s="1" t="s">
+        <v>82</v>
+      </c>
+    </row>
+    <row r="74" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A74">
+        <v>73</v>
+      </c>
+      <c r="B74" t="s">
+        <v>196</v>
+      </c>
+      <c r="C74" t="s">
+        <v>268</v>
+      </c>
+      <c r="D74" t="s">
+        <v>269</v>
+      </c>
+      <c r="E74" t="s">
+        <v>327</v>
+      </c>
+      <c r="F74" s="1" t="s">
+        <v>82</v>
+      </c>
+      <c r="G74" s="1" t="s">
+        <v>82</v>
+      </c>
+    </row>
+    <row r="75" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A75">
+        <v>74</v>
+      </c>
+      <c r="B75" t="s">
+        <v>196</v>
+      </c>
+      <c r="C75" t="s">
+        <v>270</v>
+      </c>
+      <c r="D75" t="s">
+        <v>271</v>
+      </c>
+      <c r="E75" t="s">
+        <v>272</v>
+      </c>
+      <c r="F75" s="1" t="s">
+        <v>82</v>
+      </c>
+      <c r="G75" s="1" t="s">
+        <v>82</v>
+      </c>
+    </row>
+    <row r="76" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A76">
+        <v>75</v>
+      </c>
+      <c r="B76" t="s">
+        <v>196</v>
+      </c>
+      <c r="C76" t="s">
+        <v>273</v>
+      </c>
+      <c r="D76" t="s">
+        <v>274</v>
+      </c>
+      <c r="E76" t="s">
+        <v>275</v>
+      </c>
+      <c r="F76" s="1" t="s">
+        <v>82</v>
+      </c>
+      <c r="G76" s="1" t="s">
+        <v>82</v>
+      </c>
+    </row>
+    <row r="77" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A77">
+        <v>76</v>
+      </c>
+      <c r="B77" t="s">
+        <v>196</v>
+      </c>
+      <c r="C77" t="s">
+        <v>276</v>
+      </c>
+      <c r="D77" t="s">
+        <v>277</v>
+      </c>
+      <c r="E77" s="1" t="s">
+        <v>82</v>
+      </c>
+      <c r="F77" s="1" t="s">
+        <v>82</v>
+      </c>
+      <c r="G77" s="1" t="s">
+        <v>82</v>
+      </c>
+    </row>
+    <row r="78" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A78">
+        <v>77</v>
+      </c>
+      <c r="B78" t="s">
+        <v>196</v>
+      </c>
+      <c r="C78" t="s">
+        <v>278</v>
+      </c>
+      <c r="D78" t="s">
+        <v>279</v>
+      </c>
+      <c r="E78" s="1" t="s">
+        <v>82</v>
+      </c>
+      <c r="F78" s="1" t="s">
+        <v>82</v>
+      </c>
+      <c r="G78" s="1" t="s">
+        <v>82</v>
+      </c>
+    </row>
+    <row r="79" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A79">
+        <v>78</v>
+      </c>
+      <c r="B79" t="s">
+        <v>196</v>
+      </c>
+      <c r="C79" t="s">
+        <v>280</v>
+      </c>
+      <c r="D79" t="s">
+        <v>281</v>
+      </c>
+      <c r="E79" t="s">
+        <v>282</v>
+      </c>
+      <c r="F79" s="1" t="s">
+        <v>82</v>
+      </c>
+      <c r="G79" s="1" t="s">
+        <v>82</v>
+      </c>
+    </row>
+    <row r="80" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A80">
+        <v>79</v>
+      </c>
+      <c r="B80" t="s">
+        <v>196</v>
+      </c>
+      <c r="C80" t="s">
+        <v>283</v>
+      </c>
+      <c r="D80" s="1" t="s">
+        <v>82</v>
+      </c>
+      <c r="E80" s="1" t="s">
+        <v>82</v>
+      </c>
+      <c r="F80" s="1" t="s">
+        <v>82</v>
+      </c>
+      <c r="G80" s="1" t="s">
+        <v>82</v>
+      </c>
+    </row>
+    <row r="81" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A81">
+        <v>80</v>
+      </c>
+      <c r="B81" t="s">
+        <v>196</v>
+      </c>
+      <c r="C81" t="s">
+        <v>284</v>
+      </c>
+      <c r="D81" t="s">
+        <v>285</v>
+      </c>
+      <c r="E81" t="s">
+        <v>328</v>
+      </c>
+      <c r="F81" s="1" t="s">
+        <v>82</v>
+      </c>
+      <c r="G81" s="1" t="s">
+        <v>82</v>
+      </c>
+    </row>
+    <row r="82" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A82">
+        <v>81</v>
+      </c>
+      <c r="B82" t="s">
+        <v>196</v>
+      </c>
+      <c r="C82" t="s">
+        <v>286</v>
+      </c>
+      <c r="D82" t="s">
+        <v>287</v>
+      </c>
+      <c r="E82" t="s">
+        <v>288</v>
+      </c>
+      <c r="F82" s="1" t="s">
+        <v>82</v>
+      </c>
+      <c r="G82" s="1" t="s">
+        <v>82</v>
+      </c>
+    </row>
+    <row r="83" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A83">
+        <v>82</v>
+      </c>
+      <c r="B83" t="s">
+        <v>196</v>
+      </c>
+      <c r="C83" t="s">
+        <v>289</v>
+      </c>
+      <c r="D83" t="s">
+        <v>290</v>
+      </c>
+      <c r="E83" t="s">
+        <v>291</v>
+      </c>
+      <c r="F83" s="1" t="s">
+        <v>82</v>
+      </c>
+      <c r="G83" s="1" t="s">
+        <v>82</v>
+      </c>
+    </row>
+    <row r="84" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A84">
+        <v>83</v>
+      </c>
+      <c r="B84" t="s">
+        <v>196</v>
+      </c>
+      <c r="C84" t="s">
+        <v>292</v>
+      </c>
+      <c r="D84" t="s">
+        <v>293</v>
+      </c>
+      <c r="E84" t="s">
+        <v>294</v>
+      </c>
+      <c r="F84" s="1" t="s">
+        <v>82</v>
+      </c>
+      <c r="G84" s="1" t="s">
+        <v>82</v>
+      </c>
+    </row>
+    <row r="85" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A85">
+        <v>84</v>
+      </c>
+      <c r="B85" t="s">
+        <v>196</v>
+      </c>
+      <c r="C85" t="s">
+        <v>295</v>
+      </c>
+      <c r="D85" t="s">
+        <v>296</v>
+      </c>
+      <c r="E85" t="s">
+        <v>329</v>
+      </c>
+      <c r="F85" s="1" t="s">
+        <v>82</v>
+      </c>
+      <c r="G85" s="1" t="s">
+        <v>82</v>
+      </c>
+    </row>
+    <row r="86" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A86">
+        <v>85</v>
+      </c>
+      <c r="B86" t="s">
+        <v>196</v>
+      </c>
+      <c r="C86" t="s">
+        <v>297</v>
+      </c>
+      <c r="D86" t="s">
+        <v>298</v>
+      </c>
+      <c r="E86" t="s">
+        <v>299</v>
+      </c>
+      <c r="F86" s="1" t="s">
+        <v>82</v>
+      </c>
+      <c r="G86" s="1" t="s">
+        <v>82</v>
+      </c>
+    </row>
+    <row r="87" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A87">
+        <v>86</v>
+      </c>
+      <c r="B87" t="s">
+        <v>196</v>
+      </c>
+      <c r="C87" t="s">
+        <v>300</v>
+      </c>
+      <c r="D87" t="s">
+        <v>301</v>
+      </c>
+      <c r="E87" t="s">
+        <v>302</v>
+      </c>
+      <c r="F87" s="1" t="s">
+        <v>82</v>
+      </c>
+      <c r="G87" s="1" t="s">
+        <v>82</v>
+      </c>
+    </row>
+    <row r="88" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A88">
+        <v>87</v>
+      </c>
+      <c r="B88" t="s">
+        <v>196</v>
+      </c>
+      <c r="C88" t="s">
+        <v>303</v>
+      </c>
+      <c r="D88" t="s">
+        <v>304</v>
+      </c>
+      <c r="E88" t="s">
+        <v>305</v>
+      </c>
+      <c r="F88" s="1" t="s">
+        <v>82</v>
+      </c>
+      <c r="G88" s="1" t="s">
+        <v>82</v>
+      </c>
+    </row>
+    <row r="89" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A89">
+        <v>88</v>
+      </c>
+      <c r="B89" t="s">
+        <v>196</v>
+      </c>
+      <c r="C89" t="s">
+        <v>306</v>
+      </c>
+      <c r="D89" t="s">
+        <v>307</v>
+      </c>
+      <c r="E89" t="s">
+        <v>308</v>
+      </c>
+      <c r="F89" s="1" t="s">
+        <v>82</v>
+      </c>
+      <c r="G89" s="1" t="s">
+        <v>82</v>
       </c>
     </row>
   </sheetData>

--- a/2- BB.DD. SERVICIOS Y UNIDADES/BBDD SERVICIOS Y UNIDADES.xlsx
+++ b/2- BB.DD. SERVICIOS Y UNIDADES/BBDD SERVICIOS Y UNIDADES.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\IPLACEX\Año 2\PRÁCTICA IPLACEX\PLATAFORMA PASANTÍAS\GITHUB\2- BB.DD. SERVICIOS Y UNIDADES\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{8BD0C93C-BE60-42FA-A401-1CC497734224}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{D7EB8174-AF74-425B-93AB-6477E2A8F7EC}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{7936E908-9EDA-4102-87A8-C4382552261F}"/>
+    <workbookView xWindow="-28920" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{7936E908-9EDA-4102-87A8-C4382552261F}"/>
   </bookViews>
   <sheets>
     <sheet name="Hoja1" sheetId="1" r:id="rId1"/>
@@ -39,7 +39,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="536" uniqueCount="330">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="572" uniqueCount="357">
   <si>
     <t>id</t>
   </si>
@@ -338,12 +338,6 @@
     <t>patricia.arancibia@redsalud.gob.cl</t>
   </si>
   <si>
-    <t>dra. roxana fuentes cartes</t>
-  </si>
-  <si>
-    <t>roxana.fuentes@redsalud.gob.cl</t>
-  </si>
-  <si>
     <t>dra. soledad bertoló pérez</t>
   </si>
   <si>
@@ -467,9 +461,6 @@
     <t>maritza.malhue@redsalud.gob.cl</t>
   </si>
   <si>
-    <t>subdirección</t>
-  </si>
-  <si>
     <t>médica</t>
   </si>
   <si>
@@ -1029,6 +1020,96 @@
   </si>
   <si>
     <t>shirley.rustom@redsalud.gob.cl</t>
+  </si>
+  <si>
+    <t>subdirección/staff</t>
+  </si>
+  <si>
+    <t>desarrollo de gestión de las personas</t>
+  </si>
+  <si>
+    <t>gestión de las personas</t>
+  </si>
+  <si>
+    <t>miriam soto vásquez</t>
+  </si>
+  <si>
+    <t>miriam.sotov@redsalud.gob.cl</t>
+  </si>
+  <si>
+    <t>sandra felipe lobos</t>
+  </si>
+  <si>
+    <t>sandra.felipe@redsalud.gob.cl</t>
+  </si>
+  <si>
+    <t>calidad de vida laboral</t>
+  </si>
+  <si>
+    <t>mariela gallardo viñals</t>
+  </si>
+  <si>
+    <t>mariela.gallardo@redsalud.gob.cl</t>
+  </si>
+  <si>
+    <t>iris reyes mora</t>
+  </si>
+  <si>
+    <t>iris.reyes@redsalud.gob.cl</t>
+  </si>
+  <si>
+    <t>reclutamiento y selección</t>
+  </si>
+  <si>
+    <t>valentina molina hansen</t>
+  </si>
+  <si>
+    <t>valentina.molinah@redsalud.gob.cl</t>
+  </si>
+  <si>
+    <t>ussoma</t>
+  </si>
+  <si>
+    <t>ariel dávila quijón</t>
+  </si>
+  <si>
+    <t>ariel.davila.q@redsalud.gob.cl</t>
+  </si>
+  <si>
+    <t>atención social al personal y bienestar</t>
+  </si>
+  <si>
+    <t>verónica pérez gutiérrez</t>
+  </si>
+  <si>
+    <t>veronica.perez.gutierrez@redsalud.gob.cl</t>
+  </si>
+  <si>
+    <t>adriana toledo carrasco</t>
+  </si>
+  <si>
+    <t>adriana.toledo@redsalud.gob.cl</t>
+  </si>
+  <si>
+    <t>capacitación</t>
+  </si>
+  <si>
+    <t>romy geissbuhler acuña</t>
+  </si>
+  <si>
+    <t>romy.geissbuhler@redsalud.gob.cl</t>
+  </si>
+  <si>
+    <t>marisol lara valladares</t>
+  </si>
+  <si>
+    <t>marisol.lara@redsalud.gob.cl</t>
+  </si>
+  <si>
+    <t>dr. víctor aliste</t>
+  </si>
+  <si>
+    <t>victor. aliste.c@redsalud.gob.cl</t>
   </si>
 </sst>
 </file>
@@ -1070,9 +1151,12 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="2">
+  <cellXfs count="3">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="2" borderId="0" xfId="0" applyFill="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -1407,10 +1491,10 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{37800E50-6288-4855-903E-7D1C9ED078D0}">
-  <dimension ref="A1:H89"/>
+  <dimension ref="A1:H151"/>
   <sheetFormatPr baseColWidth="10" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="1" max="1" width="3" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="4" bestFit="1" customWidth="1"/>
     <col min="2" max="2" width="35" bestFit="1" customWidth="1"/>
     <col min="3" max="3" width="45.140625" bestFit="1" customWidth="1"/>
     <col min="4" max="4" width="33.140625" bestFit="1" customWidth="1"/>
@@ -1424,10 +1508,10 @@
         <v>0</v>
       </c>
       <c r="B1" t="s">
-        <v>142</v>
+        <v>327</v>
       </c>
       <c r="C1" t="s">
-        <v>171</v>
+        <v>168</v>
       </c>
       <c r="D1" t="s">
         <v>1</v>
@@ -1450,10 +1534,10 @@
         <v>1</v>
       </c>
       <c r="B2" t="s">
-        <v>143</v>
+        <v>140</v>
       </c>
       <c r="C2" t="s">
-        <v>160</v>
+        <v>157</v>
       </c>
       <c r="D2" t="s">
         <v>6</v>
@@ -1473,10 +1557,10 @@
         <v>2</v>
       </c>
       <c r="B3" t="s">
-        <v>143</v>
+        <v>140</v>
       </c>
       <c r="C3" t="s">
-        <v>161</v>
+        <v>158</v>
       </c>
       <c r="D3" t="s">
         <v>10</v>
@@ -1496,10 +1580,10 @@
         <v>3</v>
       </c>
       <c r="B4" t="s">
-        <v>143</v>
+        <v>140</v>
       </c>
       <c r="C4" t="s">
-        <v>116</v>
+        <v>114</v>
       </c>
       <c r="D4" t="s">
         <v>63</v>
@@ -1519,10 +1603,10 @@
         <v>4</v>
       </c>
       <c r="B5" t="s">
-        <v>143</v>
+        <v>140</v>
       </c>
       <c r="C5" t="s">
-        <v>162</v>
+        <v>159</v>
       </c>
       <c r="D5" t="s">
         <v>64</v>
@@ -1542,10 +1626,10 @@
         <v>5</v>
       </c>
       <c r="B6" t="s">
-        <v>143</v>
+        <v>140</v>
       </c>
       <c r="C6" t="s">
-        <v>163</v>
+        <v>160</v>
       </c>
       <c r="D6" t="s">
         <v>65</v>
@@ -1565,10 +1649,10 @@
         <v>6</v>
       </c>
       <c r="B7" t="s">
-        <v>143</v>
+        <v>140</v>
       </c>
       <c r="C7" t="s">
-        <v>164</v>
+        <v>161</v>
       </c>
       <c r="D7" t="s">
         <v>23</v>
@@ -1588,10 +1672,10 @@
         <v>7</v>
       </c>
       <c r="B8" t="s">
-        <v>143</v>
+        <v>140</v>
       </c>
       <c r="C8" t="s">
-        <v>165</v>
+        <v>162</v>
       </c>
       <c r="D8" t="s">
         <v>27</v>
@@ -1611,10 +1695,10 @@
         <v>8</v>
       </c>
       <c r="B9" t="s">
-        <v>143</v>
+        <v>140</v>
       </c>
       <c r="C9" t="s">
-        <v>107</v>
+        <v>105</v>
       </c>
       <c r="D9" t="s">
         <v>31</v>
@@ -1634,10 +1718,10 @@
         <v>9</v>
       </c>
       <c r="B10" t="s">
-        <v>143</v>
+        <v>140</v>
       </c>
       <c r="C10" t="s">
-        <v>166</v>
+        <v>163</v>
       </c>
       <c r="D10" t="s">
         <v>66</v>
@@ -1657,10 +1741,10 @@
         <v>10</v>
       </c>
       <c r="B11" t="s">
-        <v>143</v>
+        <v>140</v>
       </c>
       <c r="C11" t="s">
-        <v>167</v>
+        <v>164</v>
       </c>
       <c r="D11" t="s">
         <v>38</v>
@@ -1680,10 +1764,10 @@
         <v>11</v>
       </c>
       <c r="B12" t="s">
-        <v>143</v>
+        <v>140</v>
       </c>
       <c r="C12" t="s">
-        <v>168</v>
+        <v>165</v>
       </c>
       <c r="D12" t="s">
         <v>42</v>
@@ -1691,11 +1775,11 @@
       <c r="E12" t="s">
         <v>43</v>
       </c>
-      <c r="F12" s="1" t="s">
-        <v>82</v>
-      </c>
-      <c r="G12" s="1" t="s">
-        <v>82</v>
+      <c r="F12" t="s">
+        <v>44</v>
+      </c>
+      <c r="G12" t="s">
+        <v>44</v>
       </c>
     </row>
     <row r="13" spans="1:8" x14ac:dyDescent="0.25">
@@ -1703,10 +1787,10 @@
         <v>12</v>
       </c>
       <c r="B13" t="s">
-        <v>143</v>
+        <v>140</v>
       </c>
       <c r="C13" t="s">
-        <v>169</v>
+        <v>166</v>
       </c>
       <c r="D13" t="s">
         <v>45</v>
@@ -1726,10 +1810,10 @@
         <v>13</v>
       </c>
       <c r="B14" t="s">
-        <v>143</v>
+        <v>140</v>
       </c>
       <c r="C14" t="s">
-        <v>170</v>
+        <v>167</v>
       </c>
       <c r="D14" t="s">
         <v>49</v>
@@ -1749,7 +1833,7 @@
         <v>14</v>
       </c>
       <c r="B15" t="s">
-        <v>143</v>
+        <v>140</v>
       </c>
       <c r="C15" t="s">
         <v>79</v>
@@ -1772,7 +1856,7 @@
         <v>15</v>
       </c>
       <c r="B16" t="s">
-        <v>143</v>
+        <v>140</v>
       </c>
       <c r="C16" t="s">
         <v>55</v>
@@ -1795,7 +1879,7 @@
         <v>16</v>
       </c>
       <c r="B17" t="s">
-        <v>143</v>
+        <v>140</v>
       </c>
       <c r="C17" t="s">
         <v>57</v>
@@ -1818,7 +1902,7 @@
         <v>17</v>
       </c>
       <c r="B18" t="s">
-        <v>143</v>
+        <v>140</v>
       </c>
       <c r="C18" t="s">
         <v>60</v>
@@ -1829,11 +1913,11 @@
       <c r="E18" t="s">
         <v>62</v>
       </c>
-      <c r="F18" s="1" t="s">
-        <v>82</v>
-      </c>
-      <c r="G18" s="1" t="s">
-        <v>82</v>
+      <c r="F18" t="s">
+        <v>44</v>
+      </c>
+      <c r="G18" t="s">
+        <v>44</v>
       </c>
     </row>
     <row r="19" spans="1:7" x14ac:dyDescent="0.25">
@@ -1841,7 +1925,7 @@
         <v>18</v>
       </c>
       <c r="B19" t="s">
-        <v>143</v>
+        <v>140</v>
       </c>
       <c r="C19" t="s">
         <v>68</v>
@@ -1864,7 +1948,7 @@
         <v>19</v>
       </c>
       <c r="B20" t="s">
-        <v>143</v>
+        <v>140</v>
       </c>
       <c r="C20" t="s">
         <v>71</v>
@@ -1887,10 +1971,10 @@
         <v>20</v>
       </c>
       <c r="B21" t="s">
-        <v>143</v>
+        <v>140</v>
       </c>
       <c r="C21" t="s">
-        <v>159</v>
+        <v>156</v>
       </c>
       <c r="D21" t="s">
         <v>74</v>
@@ -1910,7 +1994,7 @@
         <v>21</v>
       </c>
       <c r="B22" t="s">
-        <v>143</v>
+        <v>140</v>
       </c>
       <c r="C22" t="s">
         <v>76</v>
@@ -1933,7 +2017,7 @@
         <v>22</v>
       </c>
       <c r="B23" t="s">
-        <v>143</v>
+        <v>140</v>
       </c>
       <c r="C23" t="s">
         <v>79</v>
@@ -1956,22 +2040,22 @@
         <v>23</v>
       </c>
       <c r="B24" t="s">
-        <v>143</v>
+        <v>140</v>
       </c>
       <c r="C24" t="s">
-        <v>144</v>
+        <v>141</v>
       </c>
       <c r="D24" t="s">
+        <v>189</v>
+      </c>
+      <c r="E24" t="s">
+        <v>190</v>
+      </c>
+      <c r="F24" t="s">
+        <v>191</v>
+      </c>
+      <c r="G24" t="s">
         <v>192</v>
-      </c>
-      <c r="E24" t="s">
-        <v>193</v>
-      </c>
-      <c r="F24" t="s">
-        <v>194</v>
-      </c>
-      <c r="G24" t="s">
-        <v>195</v>
       </c>
     </row>
     <row r="25" spans="1:7" x14ac:dyDescent="0.25">
@@ -1979,10 +2063,10 @@
         <v>24</v>
       </c>
       <c r="B25" t="s">
-        <v>143</v>
+        <v>140</v>
       </c>
       <c r="C25" t="s">
-        <v>158</v>
+        <v>155</v>
       </c>
       <c r="D25" t="s">
         <v>83</v>
@@ -2002,10 +2086,10 @@
         <v>25</v>
       </c>
       <c r="B26" t="s">
-        <v>143</v>
+        <v>140</v>
       </c>
       <c r="C26" t="s">
-        <v>145</v>
+        <v>142</v>
       </c>
       <c r="D26" t="s">
         <v>87</v>
@@ -2025,10 +2109,10 @@
         <v>26</v>
       </c>
       <c r="B27" t="s">
+        <v>140</v>
+      </c>
+      <c r="C27" t="s">
         <v>143</v>
-      </c>
-      <c r="C27" t="s">
-        <v>146</v>
       </c>
       <c r="D27" t="s">
         <v>91</v>
@@ -2048,10 +2132,10 @@
         <v>27</v>
       </c>
       <c r="B28" t="s">
-        <v>143</v>
+        <v>140</v>
       </c>
       <c r="C28" t="s">
-        <v>147</v>
+        <v>144</v>
       </c>
       <c r="D28" t="s">
         <v>95</v>
@@ -2071,22 +2155,22 @@
         <v>28</v>
       </c>
       <c r="B29" t="s">
-        <v>143</v>
+        <v>140</v>
       </c>
       <c r="C29" t="s">
-        <v>148</v>
+        <v>145</v>
       </c>
       <c r="D29" t="s">
-        <v>99</v>
+        <v>355</v>
       </c>
       <c r="E29" t="s">
-        <v>100</v>
-      </c>
-      <c r="F29" s="1" t="s">
-        <v>82</v>
-      </c>
-      <c r="G29" s="1" t="s">
-        <v>82</v>
+        <v>356</v>
+      </c>
+      <c r="F29" t="s">
+        <v>44</v>
+      </c>
+      <c r="G29" t="s">
+        <v>44</v>
       </c>
     </row>
     <row r="30" spans="1:7" x14ac:dyDescent="0.25">
@@ -2094,22 +2178,22 @@
         <v>29</v>
       </c>
       <c r="B30" t="s">
-        <v>143</v>
+        <v>140</v>
       </c>
       <c r="C30" t="s">
-        <v>149</v>
+        <v>146</v>
       </c>
       <c r="D30" t="s">
+        <v>99</v>
+      </c>
+      <c r="E30" t="s">
+        <v>100</v>
+      </c>
+      <c r="F30" t="s">
         <v>101</v>
       </c>
-      <c r="E30" t="s">
+      <c r="G30" t="s">
         <v>102</v>
-      </c>
-      <c r="F30" t="s">
-        <v>103</v>
-      </c>
-      <c r="G30" t="s">
-        <v>104</v>
       </c>
     </row>
     <row r="31" spans="1:7" x14ac:dyDescent="0.25">
@@ -2117,22 +2201,22 @@
         <v>30</v>
       </c>
       <c r="B31" t="s">
-        <v>143</v>
+        <v>140</v>
       </c>
       <c r="C31" t="s">
-        <v>150</v>
+        <v>147</v>
       </c>
       <c r="D31" t="s">
-        <v>105</v>
+        <v>103</v>
       </c>
       <c r="E31" t="s">
-        <v>106</v>
-      </c>
-      <c r="F31" s="1" t="s">
-        <v>82</v>
-      </c>
-      <c r="G31" s="1" t="s">
-        <v>82</v>
+        <v>104</v>
+      </c>
+      <c r="F31" t="s">
+        <v>44</v>
+      </c>
+      <c r="G31" t="s">
+        <v>44</v>
       </c>
     </row>
     <row r="32" spans="1:7" x14ac:dyDescent="0.25">
@@ -2140,22 +2224,22 @@
         <v>31</v>
       </c>
       <c r="B32" t="s">
-        <v>143</v>
+        <v>140</v>
       </c>
       <c r="C32" t="s">
-        <v>151</v>
+        <v>148</v>
       </c>
       <c r="D32" t="s">
+        <v>106</v>
+      </c>
+      <c r="E32" t="s">
+        <v>107</v>
+      </c>
+      <c r="F32" t="s">
         <v>108</v>
       </c>
-      <c r="E32" t="s">
+      <c r="G32" t="s">
         <v>109</v>
-      </c>
-      <c r="F32" t="s">
-        <v>110</v>
-      </c>
-      <c r="G32" t="s">
-        <v>111</v>
       </c>
     </row>
     <row r="33" spans="1:7" x14ac:dyDescent="0.25">
@@ -2163,22 +2247,22 @@
         <v>32</v>
       </c>
       <c r="B33" t="s">
-        <v>143</v>
+        <v>140</v>
       </c>
       <c r="C33" t="s">
-        <v>152</v>
+        <v>149</v>
       </c>
       <c r="D33" t="s">
+        <v>110</v>
+      </c>
+      <c r="E33" t="s">
+        <v>111</v>
+      </c>
+      <c r="F33" t="s">
         <v>112</v>
       </c>
-      <c r="E33" t="s">
+      <c r="G33" t="s">
         <v>113</v>
-      </c>
-      <c r="F33" t="s">
-        <v>114</v>
-      </c>
-      <c r="G33" t="s">
-        <v>115</v>
       </c>
     </row>
     <row r="34" spans="1:7" x14ac:dyDescent="0.25">
@@ -2186,22 +2270,22 @@
         <v>33</v>
       </c>
       <c r="B34" t="s">
-        <v>143</v>
+        <v>140</v>
       </c>
       <c r="C34" t="s">
-        <v>153</v>
+        <v>150</v>
       </c>
       <c r="D34" t="s">
+        <v>115</v>
+      </c>
+      <c r="E34" t="s">
+        <v>116</v>
+      </c>
+      <c r="F34" t="s">
         <v>117</v>
       </c>
-      <c r="E34" t="s">
+      <c r="G34" t="s">
         <v>118</v>
-      </c>
-      <c r="F34" t="s">
-        <v>119</v>
-      </c>
-      <c r="G34" t="s">
-        <v>120</v>
       </c>
     </row>
     <row r="35" spans="1:7" x14ac:dyDescent="0.25">
@@ -2209,22 +2293,22 @@
         <v>34</v>
       </c>
       <c r="B35" t="s">
-        <v>143</v>
+        <v>140</v>
       </c>
       <c r="C35" t="s">
-        <v>154</v>
+        <v>151</v>
       </c>
       <c r="D35" t="s">
+        <v>119</v>
+      </c>
+      <c r="E35" t="s">
+        <v>120</v>
+      </c>
+      <c r="F35" t="s">
         <v>121</v>
       </c>
-      <c r="E35" t="s">
+      <c r="G35" t="s">
         <v>122</v>
-      </c>
-      <c r="F35" t="s">
-        <v>123</v>
-      </c>
-      <c r="G35" t="s">
-        <v>124</v>
       </c>
     </row>
     <row r="36" spans="1:7" x14ac:dyDescent="0.25">
@@ -2232,22 +2316,22 @@
         <v>35</v>
       </c>
       <c r="B36" t="s">
-        <v>143</v>
+        <v>140</v>
       </c>
       <c r="C36" t="s">
-        <v>155</v>
+        <v>152</v>
       </c>
       <c r="D36" t="s">
+        <v>123</v>
+      </c>
+      <c r="E36" t="s">
+        <v>124</v>
+      </c>
+      <c r="F36" t="s">
         <v>125</v>
       </c>
-      <c r="E36" t="s">
+      <c r="G36" t="s">
         <v>126</v>
-      </c>
-      <c r="F36" t="s">
-        <v>127</v>
-      </c>
-      <c r="G36" t="s">
-        <v>128</v>
       </c>
     </row>
     <row r="37" spans="1:7" x14ac:dyDescent="0.25">
@@ -2255,22 +2339,22 @@
         <v>36</v>
       </c>
       <c r="B37" t="s">
-        <v>143</v>
+        <v>140</v>
       </c>
       <c r="C37" t="s">
-        <v>156</v>
+        <v>153</v>
       </c>
       <c r="D37" t="s">
+        <v>127</v>
+      </c>
+      <c r="E37" t="s">
+        <v>128</v>
+      </c>
+      <c r="F37" t="s">
         <v>129</v>
       </c>
-      <c r="E37" t="s">
+      <c r="G37" t="s">
         <v>130</v>
-      </c>
-      <c r="F37" t="s">
-        <v>131</v>
-      </c>
-      <c r="G37" t="s">
-        <v>132</v>
       </c>
     </row>
     <row r="38" spans="1:7" x14ac:dyDescent="0.25">
@@ -2278,22 +2362,22 @@
         <v>37</v>
       </c>
       <c r="B38" t="s">
-        <v>143</v>
+        <v>140</v>
       </c>
       <c r="C38" t="s">
-        <v>157</v>
+        <v>154</v>
       </c>
       <c r="D38" t="s">
+        <v>131</v>
+      </c>
+      <c r="E38" t="s">
+        <v>132</v>
+      </c>
+      <c r="F38" t="s">
         <v>133</v>
       </c>
-      <c r="E38" t="s">
+      <c r="G38" t="s">
         <v>134</v>
-      </c>
-      <c r="F38" t="s">
-        <v>135</v>
-      </c>
-      <c r="G38" t="s">
-        <v>136</v>
       </c>
     </row>
     <row r="39" spans="1:7" x14ac:dyDescent="0.25">
@@ -2301,22 +2385,22 @@
         <v>38</v>
       </c>
       <c r="B39" t="s">
-        <v>143</v>
+        <v>140</v>
       </c>
       <c r="C39" t="s">
+        <v>135</v>
+      </c>
+      <c r="D39" t="s">
+        <v>136</v>
+      </c>
+      <c r="E39" t="s">
         <v>137</v>
       </c>
-      <c r="D39" t="s">
+      <c r="F39" t="s">
         <v>138</v>
       </c>
-      <c r="E39" t="s">
+      <c r="G39" t="s">
         <v>139</v>
-      </c>
-      <c r="F39" t="s">
-        <v>140</v>
-      </c>
-      <c r="G39" t="s">
-        <v>141</v>
       </c>
     </row>
     <row r="40" spans="1:7" x14ac:dyDescent="0.25">
@@ -2324,22 +2408,22 @@
         <v>39</v>
       </c>
       <c r="B40" t="s">
+        <v>169</v>
+      </c>
+      <c r="C40" t="s">
+        <v>170</v>
+      </c>
+      <c r="D40" t="s">
+        <v>171</v>
+      </c>
+      <c r="E40" t="s">
         <v>172</v>
       </c>
-      <c r="C40" t="s">
+      <c r="F40" t="s">
         <v>173</v>
       </c>
-      <c r="D40" t="s">
+      <c r="G40" t="s">
         <v>174</v>
-      </c>
-      <c r="E40" t="s">
-        <v>175</v>
-      </c>
-      <c r="F40" t="s">
-        <v>176</v>
-      </c>
-      <c r="G40" t="s">
-        <v>177</v>
       </c>
     </row>
     <row r="41" spans="1:7" x14ac:dyDescent="0.25">
@@ -2347,22 +2431,22 @@
         <v>40</v>
       </c>
       <c r="B41" t="s">
-        <v>172</v>
+        <v>169</v>
       </c>
       <c r="C41" t="s">
+        <v>175</v>
+      </c>
+      <c r="D41" t="s">
+        <v>176</v>
+      </c>
+      <c r="E41" t="s">
+        <v>177</v>
+      </c>
+      <c r="F41" t="s">
         <v>178</v>
       </c>
-      <c r="D41" t="s">
+      <c r="G41" t="s">
         <v>179</v>
-      </c>
-      <c r="E41" t="s">
-        <v>180</v>
-      </c>
-      <c r="F41" t="s">
-        <v>181</v>
-      </c>
-      <c r="G41" t="s">
-        <v>182</v>
       </c>
     </row>
     <row r="42" spans="1:7" x14ac:dyDescent="0.25">
@@ -2370,22 +2454,22 @@
         <v>41</v>
       </c>
       <c r="B42" t="s">
-        <v>172</v>
+        <v>169</v>
       </c>
       <c r="C42" t="s">
+        <v>180</v>
+      </c>
+      <c r="D42" t="s">
+        <v>181</v>
+      </c>
+      <c r="E42" t="s">
+        <v>182</v>
+      </c>
+      <c r="F42" t="s">
         <v>183</v>
       </c>
-      <c r="D42" t="s">
+      <c r="G42" t="s">
         <v>184</v>
-      </c>
-      <c r="E42" t="s">
-        <v>185</v>
-      </c>
-      <c r="F42" t="s">
-        <v>186</v>
-      </c>
-      <c r="G42" t="s">
-        <v>187</v>
       </c>
     </row>
     <row r="43" spans="1:7" x14ac:dyDescent="0.25">
@@ -2393,19 +2477,19 @@
         <v>42</v>
       </c>
       <c r="B43" t="s">
-        <v>172</v>
+        <v>169</v>
       </c>
       <c r="C43" t="s">
+        <v>185</v>
+      </c>
+      <c r="D43" t="s">
+        <v>186</v>
+      </c>
+      <c r="E43" t="s">
+        <v>187</v>
+      </c>
+      <c r="F43" t="s">
         <v>188</v>
-      </c>
-      <c r="D43" t="s">
-        <v>189</v>
-      </c>
-      <c r="E43" t="s">
-        <v>190</v>
-      </c>
-      <c r="F43" t="s">
-        <v>191</v>
       </c>
       <c r="G43" s="1" t="s">
         <v>82</v>
@@ -2416,16 +2500,16 @@
         <v>43</v>
       </c>
       <c r="B44" t="s">
-        <v>196</v>
+        <v>193</v>
       </c>
       <c r="C44" t="s">
-        <v>197</v>
+        <v>194</v>
       </c>
       <c r="D44" t="s">
-        <v>198</v>
+        <v>195</v>
       </c>
       <c r="E44" t="s">
-        <v>309</v>
+        <v>306</v>
       </c>
       <c r="F44" s="1" t="s">
         <v>82</v>
@@ -2439,16 +2523,16 @@
         <v>44</v>
       </c>
       <c r="B45" t="s">
+        <v>193</v>
+      </c>
+      <c r="C45" t="s">
         <v>196</v>
       </c>
-      <c r="C45" t="s">
-        <v>199</v>
-      </c>
       <c r="D45" t="s">
-        <v>200</v>
+        <v>197</v>
       </c>
       <c r="E45" t="s">
-        <v>310</v>
+        <v>307</v>
       </c>
       <c r="F45" s="1" t="s">
         <v>82</v>
@@ -2462,16 +2546,16 @@
         <v>45</v>
       </c>
       <c r="B46" t="s">
-        <v>196</v>
+        <v>193</v>
       </c>
       <c r="C46" t="s">
-        <v>201</v>
+        <v>198</v>
       </c>
       <c r="D46" t="s">
-        <v>202</v>
+        <v>199</v>
       </c>
       <c r="E46" t="s">
-        <v>203</v>
+        <v>200</v>
       </c>
       <c r="F46" s="1" t="s">
         <v>82</v>
@@ -2485,16 +2569,16 @@
         <v>46</v>
       </c>
       <c r="B47" t="s">
-        <v>196</v>
+        <v>193</v>
       </c>
       <c r="C47" t="s">
-        <v>204</v>
+        <v>201</v>
       </c>
       <c r="D47" t="s">
-        <v>205</v>
+        <v>202</v>
       </c>
       <c r="E47" t="s">
-        <v>311</v>
+        <v>308</v>
       </c>
       <c r="F47" s="1" t="s">
         <v>82</v>
@@ -2508,13 +2592,13 @@
         <v>47</v>
       </c>
       <c r="B48" t="s">
-        <v>196</v>
+        <v>193</v>
       </c>
       <c r="C48" t="s">
-        <v>206</v>
+        <v>203</v>
       </c>
       <c r="D48" t="s">
-        <v>207</v>
+        <v>204</v>
       </c>
       <c r="E48" s="1" t="s">
         <v>82</v>
@@ -2531,16 +2615,16 @@
         <v>48</v>
       </c>
       <c r="B49" t="s">
-        <v>196</v>
+        <v>193</v>
       </c>
       <c r="C49" t="s">
-        <v>208</v>
+        <v>205</v>
       </c>
       <c r="D49" t="s">
-        <v>209</v>
+        <v>206</v>
       </c>
       <c r="E49" t="s">
-        <v>312</v>
+        <v>309</v>
       </c>
       <c r="F49" s="1" t="s">
         <v>82</v>
@@ -2554,16 +2638,16 @@
         <v>49</v>
       </c>
       <c r="B50" t="s">
-        <v>196</v>
+        <v>193</v>
       </c>
       <c r="C50" t="s">
-        <v>210</v>
+        <v>207</v>
       </c>
       <c r="D50" t="s">
-        <v>211</v>
+        <v>208</v>
       </c>
       <c r="E50" t="s">
-        <v>212</v>
+        <v>209</v>
       </c>
       <c r="F50" s="1" t="s">
         <v>82</v>
@@ -2577,16 +2661,16 @@
         <v>50</v>
       </c>
       <c r="B51" t="s">
-        <v>196</v>
+        <v>193</v>
       </c>
       <c r="C51" t="s">
-        <v>213</v>
+        <v>210</v>
       </c>
       <c r="D51" t="s">
-        <v>214</v>
+        <v>211</v>
       </c>
       <c r="E51" t="s">
-        <v>313</v>
+        <v>310</v>
       </c>
       <c r="F51" s="1" t="s">
         <v>82</v>
@@ -2600,16 +2684,16 @@
         <v>51</v>
       </c>
       <c r="B52" t="s">
-        <v>196</v>
+        <v>193</v>
       </c>
       <c r="C52" t="s">
-        <v>215</v>
+        <v>212</v>
       </c>
       <c r="D52" t="s">
-        <v>216</v>
+        <v>213</v>
       </c>
       <c r="E52" t="s">
-        <v>314</v>
+        <v>311</v>
       </c>
       <c r="F52" s="1" t="s">
         <v>82</v>
@@ -2623,16 +2707,16 @@
         <v>52</v>
       </c>
       <c r="B53" t="s">
-        <v>196</v>
+        <v>193</v>
       </c>
       <c r="C53" t="s">
-        <v>217</v>
+        <v>214</v>
       </c>
       <c r="D53" t="s">
-        <v>218</v>
+        <v>215</v>
       </c>
       <c r="E53" t="s">
-        <v>315</v>
+        <v>312</v>
       </c>
       <c r="F53" s="1" t="s">
         <v>82</v>
@@ -2646,16 +2730,16 @@
         <v>53</v>
       </c>
       <c r="B54" t="s">
-        <v>196</v>
+        <v>193</v>
       </c>
       <c r="C54" t="s">
-        <v>219</v>
+        <v>216</v>
       </c>
       <c r="D54" t="s">
-        <v>220</v>
+        <v>217</v>
       </c>
       <c r="E54" t="s">
-        <v>316</v>
+        <v>313</v>
       </c>
       <c r="F54" s="1" t="s">
         <v>82</v>
@@ -2669,16 +2753,16 @@
         <v>54</v>
       </c>
       <c r="B55" t="s">
-        <v>196</v>
+        <v>193</v>
       </c>
       <c r="C55" t="s">
-        <v>221</v>
+        <v>218</v>
       </c>
       <c r="D55" t="s">
-        <v>222</v>
+        <v>219</v>
       </c>
       <c r="E55" t="s">
-        <v>223</v>
+        <v>220</v>
       </c>
       <c r="F55" s="1" t="s">
         <v>82</v>
@@ -2692,16 +2776,16 @@
         <v>55</v>
       </c>
       <c r="B56" t="s">
-        <v>196</v>
+        <v>193</v>
       </c>
       <c r="C56" t="s">
-        <v>224</v>
+        <v>221</v>
       </c>
       <c r="D56" t="s">
-        <v>225</v>
+        <v>222</v>
       </c>
       <c r="E56" t="s">
-        <v>317</v>
+        <v>314</v>
       </c>
       <c r="F56" s="1" t="s">
         <v>82</v>
@@ -2715,16 +2799,16 @@
         <v>56</v>
       </c>
       <c r="B57" t="s">
-        <v>196</v>
+        <v>193</v>
       </c>
       <c r="C57" t="s">
-        <v>226</v>
+        <v>223</v>
       </c>
       <c r="D57" t="s">
-        <v>227</v>
+        <v>224</v>
       </c>
       <c r="E57" t="s">
-        <v>318</v>
+        <v>315</v>
       </c>
       <c r="F57" s="1" t="s">
         <v>82</v>
@@ -2738,16 +2822,16 @@
         <v>57</v>
       </c>
       <c r="B58" t="s">
-        <v>196</v>
+        <v>193</v>
       </c>
       <c r="C58" t="s">
-        <v>228</v>
+        <v>225</v>
       </c>
       <c r="D58" t="s">
-        <v>229</v>
+        <v>226</v>
       </c>
       <c r="E58" t="s">
-        <v>319</v>
+        <v>316</v>
       </c>
       <c r="F58" s="1" t="s">
         <v>82</v>
@@ -2761,16 +2845,16 @@
         <v>58</v>
       </c>
       <c r="B59" t="s">
-        <v>196</v>
+        <v>193</v>
       </c>
       <c r="C59" t="s">
-        <v>230</v>
+        <v>227</v>
       </c>
       <c r="D59" t="s">
-        <v>231</v>
+        <v>228</v>
       </c>
       <c r="E59" t="s">
-        <v>232</v>
+        <v>229</v>
       </c>
       <c r="F59" s="1" t="s">
         <v>82</v>
@@ -2784,16 +2868,16 @@
         <v>59</v>
       </c>
       <c r="B60" t="s">
-        <v>196</v>
+        <v>193</v>
       </c>
       <c r="C60" t="s">
-        <v>233</v>
+        <v>230</v>
       </c>
       <c r="D60" t="s">
-        <v>234</v>
+        <v>231</v>
       </c>
       <c r="E60" t="s">
-        <v>235</v>
+        <v>232</v>
       </c>
       <c r="F60" s="1" t="s">
         <v>82</v>
@@ -2807,16 +2891,16 @@
         <v>60</v>
       </c>
       <c r="B61" t="s">
-        <v>196</v>
+        <v>193</v>
       </c>
       <c r="C61" t="s">
-        <v>236</v>
+        <v>233</v>
       </c>
       <c r="D61" t="s">
-        <v>237</v>
+        <v>234</v>
       </c>
       <c r="E61" t="s">
-        <v>320</v>
+        <v>317</v>
       </c>
       <c r="F61" s="1" t="s">
         <v>82</v>
@@ -2830,16 +2914,16 @@
         <v>61</v>
       </c>
       <c r="B62" t="s">
-        <v>196</v>
+        <v>193</v>
       </c>
       <c r="C62" t="s">
-        <v>238</v>
+        <v>235</v>
       </c>
       <c r="D62" t="s">
-        <v>239</v>
+        <v>236</v>
       </c>
       <c r="E62" t="s">
-        <v>240</v>
+        <v>237</v>
       </c>
       <c r="F62" s="1" t="s">
         <v>82</v>
@@ -2853,16 +2937,16 @@
         <v>62</v>
       </c>
       <c r="B63" t="s">
-        <v>196</v>
+        <v>193</v>
       </c>
       <c r="C63" t="s">
-        <v>241</v>
+        <v>238</v>
       </c>
       <c r="D63" t="s">
-        <v>242</v>
+        <v>239</v>
       </c>
       <c r="E63" t="s">
-        <v>243</v>
+        <v>240</v>
       </c>
       <c r="F63" s="1" t="s">
         <v>82</v>
@@ -2876,16 +2960,16 @@
         <v>63</v>
       </c>
       <c r="B64" t="s">
-        <v>196</v>
+        <v>193</v>
       </c>
       <c r="C64" t="s">
-        <v>244</v>
+        <v>241</v>
       </c>
       <c r="D64" t="s">
-        <v>245</v>
+        <v>242</v>
       </c>
       <c r="E64" t="s">
-        <v>321</v>
+        <v>318</v>
       </c>
       <c r="F64" s="1" t="s">
         <v>82</v>
@@ -2899,16 +2983,16 @@
         <v>64</v>
       </c>
       <c r="B65" t="s">
-        <v>196</v>
+        <v>193</v>
       </c>
       <c r="C65" t="s">
-        <v>246</v>
+        <v>243</v>
       </c>
       <c r="D65" t="s">
-        <v>247</v>
+        <v>244</v>
       </c>
       <c r="E65" t="s">
-        <v>322</v>
+        <v>319</v>
       </c>
       <c r="F65" s="1" t="s">
         <v>82</v>
@@ -2922,16 +3006,16 @@
         <v>65</v>
       </c>
       <c r="B66" t="s">
-        <v>196</v>
+        <v>193</v>
       </c>
       <c r="C66" t="s">
-        <v>248</v>
+        <v>245</v>
       </c>
       <c r="D66" t="s">
-        <v>249</v>
+        <v>246</v>
       </c>
       <c r="E66" t="s">
-        <v>250</v>
+        <v>247</v>
       </c>
       <c r="F66" s="1" t="s">
         <v>82</v>
@@ -2945,16 +3029,16 @@
         <v>66</v>
       </c>
       <c r="B67" t="s">
-        <v>196</v>
+        <v>193</v>
       </c>
       <c r="C67" t="s">
-        <v>251</v>
+        <v>248</v>
       </c>
       <c r="D67" t="s">
-        <v>252</v>
+        <v>249</v>
       </c>
       <c r="E67" t="s">
-        <v>323</v>
+        <v>320</v>
       </c>
       <c r="F67" s="1" t="s">
         <v>82</v>
@@ -2968,16 +3052,16 @@
         <v>67</v>
       </c>
       <c r="B68" t="s">
-        <v>196</v>
+        <v>193</v>
       </c>
       <c r="C68" t="s">
-        <v>253</v>
+        <v>250</v>
       </c>
       <c r="D68" t="s">
-        <v>254</v>
+        <v>251</v>
       </c>
       <c r="E68" t="s">
-        <v>255</v>
+        <v>252</v>
       </c>
       <c r="F68" s="1" t="s">
         <v>82</v>
@@ -2991,16 +3075,16 @@
         <v>68</v>
       </c>
       <c r="B69" t="s">
-        <v>196</v>
+        <v>193</v>
       </c>
       <c r="C69" t="s">
-        <v>256</v>
+        <v>253</v>
       </c>
       <c r="D69" t="s">
-        <v>257</v>
+        <v>254</v>
       </c>
       <c r="E69" t="s">
-        <v>324</v>
+        <v>321</v>
       </c>
       <c r="F69" s="1" t="s">
         <v>82</v>
@@ -3014,16 +3098,16 @@
         <v>69</v>
       </c>
       <c r="B70" t="s">
-        <v>196</v>
+        <v>193</v>
       </c>
       <c r="C70" t="s">
-        <v>258</v>
+        <v>255</v>
       </c>
       <c r="D70" t="s">
-        <v>259</v>
+        <v>256</v>
       </c>
       <c r="E70" t="s">
-        <v>260</v>
+        <v>257</v>
       </c>
       <c r="F70" s="1" t="s">
         <v>82</v>
@@ -3037,16 +3121,16 @@
         <v>70</v>
       </c>
       <c r="B71" t="s">
-        <v>196</v>
+        <v>193</v>
       </c>
       <c r="C71" t="s">
-        <v>261</v>
+        <v>258</v>
       </c>
       <c r="D71" t="s">
-        <v>262</v>
+        <v>259</v>
       </c>
       <c r="E71" t="s">
-        <v>325</v>
+        <v>322</v>
       </c>
       <c r="F71" s="1" t="s">
         <v>82</v>
@@ -3060,16 +3144,16 @@
         <v>71</v>
       </c>
       <c r="B72" t="s">
-        <v>196</v>
+        <v>193</v>
       </c>
       <c r="C72" t="s">
-        <v>263</v>
+        <v>260</v>
       </c>
       <c r="D72" t="s">
-        <v>264</v>
+        <v>261</v>
       </c>
       <c r="E72" t="s">
-        <v>326</v>
+        <v>323</v>
       </c>
       <c r="F72" s="1" t="s">
         <v>82</v>
@@ -3083,16 +3167,16 @@
         <v>72</v>
       </c>
       <c r="B73" t="s">
-        <v>196</v>
+        <v>193</v>
       </c>
       <c r="C73" t="s">
-        <v>265</v>
+        <v>262</v>
       </c>
       <c r="D73" t="s">
-        <v>266</v>
+        <v>263</v>
       </c>
       <c r="E73" t="s">
-        <v>267</v>
+        <v>264</v>
       </c>
       <c r="F73" s="1" t="s">
         <v>82</v>
@@ -3106,16 +3190,16 @@
         <v>73</v>
       </c>
       <c r="B74" t="s">
-        <v>196</v>
+        <v>193</v>
       </c>
       <c r="C74" t="s">
-        <v>268</v>
+        <v>265</v>
       </c>
       <c r="D74" t="s">
-        <v>269</v>
+        <v>266</v>
       </c>
       <c r="E74" t="s">
-        <v>327</v>
+        <v>324</v>
       </c>
       <c r="F74" s="1" t="s">
         <v>82</v>
@@ -3129,16 +3213,16 @@
         <v>74</v>
       </c>
       <c r="B75" t="s">
-        <v>196</v>
+        <v>193</v>
       </c>
       <c r="C75" t="s">
-        <v>270</v>
+        <v>267</v>
       </c>
       <c r="D75" t="s">
-        <v>271</v>
+        <v>268</v>
       </c>
       <c r="E75" t="s">
-        <v>272</v>
+        <v>269</v>
       </c>
       <c r="F75" s="1" t="s">
         <v>82</v>
@@ -3152,16 +3236,16 @@
         <v>75</v>
       </c>
       <c r="B76" t="s">
-        <v>196</v>
+        <v>193</v>
       </c>
       <c r="C76" t="s">
-        <v>273</v>
+        <v>270</v>
       </c>
       <c r="D76" t="s">
-        <v>274</v>
+        <v>271</v>
       </c>
       <c r="E76" t="s">
-        <v>275</v>
+        <v>272</v>
       </c>
       <c r="F76" s="1" t="s">
         <v>82</v>
@@ -3175,13 +3259,13 @@
         <v>76</v>
       </c>
       <c r="B77" t="s">
-        <v>196</v>
+        <v>193</v>
       </c>
       <c r="C77" t="s">
-        <v>276</v>
+        <v>273</v>
       </c>
       <c r="D77" t="s">
-        <v>277</v>
+        <v>274</v>
       </c>
       <c r="E77" s="1" t="s">
         <v>82</v>
@@ -3198,13 +3282,13 @@
         <v>77</v>
       </c>
       <c r="B78" t="s">
-        <v>196</v>
+        <v>193</v>
       </c>
       <c r="C78" t="s">
-        <v>278</v>
+        <v>275</v>
       </c>
       <c r="D78" t="s">
-        <v>279</v>
+        <v>276</v>
       </c>
       <c r="E78" s="1" t="s">
         <v>82</v>
@@ -3221,16 +3305,16 @@
         <v>78</v>
       </c>
       <c r="B79" t="s">
-        <v>196</v>
+        <v>193</v>
       </c>
       <c r="C79" t="s">
-        <v>280</v>
+        <v>277</v>
       </c>
       <c r="D79" t="s">
-        <v>281</v>
+        <v>278</v>
       </c>
       <c r="E79" t="s">
-        <v>282</v>
+        <v>279</v>
       </c>
       <c r="F79" s="1" t="s">
         <v>82</v>
@@ -3244,10 +3328,10 @@
         <v>79</v>
       </c>
       <c r="B80" t="s">
-        <v>196</v>
+        <v>193</v>
       </c>
       <c r="C80" t="s">
-        <v>283</v>
+        <v>280</v>
       </c>
       <c r="D80" s="1" t="s">
         <v>82</v>
@@ -3267,16 +3351,16 @@
         <v>80</v>
       </c>
       <c r="B81" t="s">
-        <v>196</v>
+        <v>193</v>
       </c>
       <c r="C81" t="s">
-        <v>284</v>
+        <v>281</v>
       </c>
       <c r="D81" t="s">
-        <v>285</v>
+        <v>282</v>
       </c>
       <c r="E81" t="s">
-        <v>328</v>
+        <v>325</v>
       </c>
       <c r="F81" s="1" t="s">
         <v>82</v>
@@ -3290,16 +3374,16 @@
         <v>81</v>
       </c>
       <c r="B82" t="s">
-        <v>196</v>
+        <v>193</v>
       </c>
       <c r="C82" t="s">
-        <v>286</v>
+        <v>283</v>
       </c>
       <c r="D82" t="s">
-        <v>287</v>
+        <v>284</v>
       </c>
       <c r="E82" t="s">
-        <v>288</v>
+        <v>285</v>
       </c>
       <c r="F82" s="1" t="s">
         <v>82</v>
@@ -3313,16 +3397,16 @@
         <v>82</v>
       </c>
       <c r="B83" t="s">
-        <v>196</v>
+        <v>193</v>
       </c>
       <c r="C83" t="s">
-        <v>289</v>
+        <v>286</v>
       </c>
       <c r="D83" t="s">
-        <v>290</v>
+        <v>287</v>
       </c>
       <c r="E83" t="s">
-        <v>291</v>
+        <v>288</v>
       </c>
       <c r="F83" s="1" t="s">
         <v>82</v>
@@ -3336,16 +3420,16 @@
         <v>83</v>
       </c>
       <c r="B84" t="s">
-        <v>196</v>
+        <v>193</v>
       </c>
       <c r="C84" t="s">
-        <v>292</v>
+        <v>289</v>
       </c>
       <c r="D84" t="s">
-        <v>293</v>
+        <v>290</v>
       </c>
       <c r="E84" t="s">
-        <v>294</v>
+        <v>291</v>
       </c>
       <c r="F84" s="1" t="s">
         <v>82</v>
@@ -3359,16 +3443,16 @@
         <v>84</v>
       </c>
       <c r="B85" t="s">
-        <v>196</v>
+        <v>193</v>
       </c>
       <c r="C85" t="s">
-        <v>295</v>
+        <v>292</v>
       </c>
       <c r="D85" t="s">
-        <v>296</v>
+        <v>293</v>
       </c>
       <c r="E85" t="s">
-        <v>329</v>
+        <v>326</v>
       </c>
       <c r="F85" s="1" t="s">
         <v>82</v>
@@ -3382,16 +3466,16 @@
         <v>85</v>
       </c>
       <c r="B86" t="s">
-        <v>196</v>
+        <v>193</v>
       </c>
       <c r="C86" t="s">
-        <v>297</v>
+        <v>294</v>
       </c>
       <c r="D86" t="s">
-        <v>298</v>
+        <v>295</v>
       </c>
       <c r="E86" t="s">
-        <v>299</v>
+        <v>296</v>
       </c>
       <c r="F86" s="1" t="s">
         <v>82</v>
@@ -3405,16 +3489,16 @@
         <v>86</v>
       </c>
       <c r="B87" t="s">
-        <v>196</v>
+        <v>193</v>
       </c>
       <c r="C87" t="s">
-        <v>300</v>
+        <v>297</v>
       </c>
       <c r="D87" t="s">
-        <v>301</v>
+        <v>298</v>
       </c>
       <c r="E87" t="s">
-        <v>302</v>
+        <v>299</v>
       </c>
       <c r="F87" s="1" t="s">
         <v>82</v>
@@ -3428,16 +3512,16 @@
         <v>87</v>
       </c>
       <c r="B88" t="s">
-        <v>196</v>
+        <v>193</v>
       </c>
       <c r="C88" t="s">
-        <v>303</v>
+        <v>300</v>
       </c>
       <c r="D88" t="s">
-        <v>304</v>
+        <v>301</v>
       </c>
       <c r="E88" t="s">
-        <v>305</v>
+        <v>302</v>
       </c>
       <c r="F88" s="1" t="s">
         <v>82</v>
@@ -3451,16 +3535,16 @@
         <v>88</v>
       </c>
       <c r="B89" t="s">
-        <v>196</v>
+        <v>193</v>
       </c>
       <c r="C89" t="s">
-        <v>306</v>
+        <v>303</v>
       </c>
       <c r="D89" t="s">
-        <v>307</v>
+        <v>304</v>
       </c>
       <c r="E89" t="s">
-        <v>308</v>
+        <v>305</v>
       </c>
       <c r="F89" s="1" t="s">
         <v>82</v>
@@ -3469,7 +3553,439 @@
         <v>82</v>
       </c>
     </row>
+    <row r="90" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A90">
+        <v>89</v>
+      </c>
+      <c r="B90" t="s">
+        <v>328</v>
+      </c>
+      <c r="C90" s="2" t="s">
+        <v>329</v>
+      </c>
+      <c r="D90" s="2" t="s">
+        <v>330</v>
+      </c>
+      <c r="E90" t="s">
+        <v>331</v>
+      </c>
+      <c r="F90" s="2" t="s">
+        <v>332</v>
+      </c>
+      <c r="G90" t="s">
+        <v>333</v>
+      </c>
+    </row>
+    <row r="91" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A91">
+        <v>90</v>
+      </c>
+      <c r="B91" t="s">
+        <v>328</v>
+      </c>
+      <c r="C91" s="2" t="s">
+        <v>334</v>
+      </c>
+      <c r="D91" s="2" t="s">
+        <v>335</v>
+      </c>
+      <c r="E91" t="s">
+        <v>336</v>
+      </c>
+      <c r="F91" s="2" t="s">
+        <v>337</v>
+      </c>
+      <c r="G91" t="s">
+        <v>338</v>
+      </c>
+    </row>
+    <row r="92" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A92">
+        <v>91</v>
+      </c>
+      <c r="B92" t="s">
+        <v>328</v>
+      </c>
+      <c r="C92" s="2" t="s">
+        <v>339</v>
+      </c>
+      <c r="D92" s="2" t="s">
+        <v>340</v>
+      </c>
+      <c r="E92" t="s">
+        <v>341</v>
+      </c>
+      <c r="F92" s="2" t="s">
+        <v>337</v>
+      </c>
+      <c r="G92" t="s">
+        <v>338</v>
+      </c>
+    </row>
+    <row r="93" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A93">
+        <v>92</v>
+      </c>
+      <c r="B93" t="s">
+        <v>328</v>
+      </c>
+      <c r="C93" s="2" t="s">
+        <v>342</v>
+      </c>
+      <c r="D93" s="2" t="s">
+        <v>343</v>
+      </c>
+      <c r="E93" t="s">
+        <v>344</v>
+      </c>
+      <c r="F93" s="2" t="s">
+        <v>337</v>
+      </c>
+      <c r="G93" t="s">
+        <v>338</v>
+      </c>
+    </row>
+    <row r="94" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A94">
+        <v>93</v>
+      </c>
+      <c r="B94" t="s">
+        <v>328</v>
+      </c>
+      <c r="C94" s="2" t="s">
+        <v>345</v>
+      </c>
+      <c r="D94" s="2" t="s">
+        <v>346</v>
+      </c>
+      <c r="E94" t="s">
+        <v>347</v>
+      </c>
+      <c r="F94" s="2" t="s">
+        <v>348</v>
+      </c>
+      <c r="G94" t="s">
+        <v>349</v>
+      </c>
+    </row>
+    <row r="95" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A95">
+        <v>94</v>
+      </c>
+      <c r="B95" t="s">
+        <v>328</v>
+      </c>
+      <c r="C95" s="2" t="s">
+        <v>350</v>
+      </c>
+      <c r="D95" s="2" t="s">
+        <v>351</v>
+      </c>
+      <c r="E95" t="s">
+        <v>352</v>
+      </c>
+      <c r="F95" s="2" t="s">
+        <v>353</v>
+      </c>
+      <c r="G95" t="s">
+        <v>354</v>
+      </c>
+    </row>
+    <row r="96" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A96">
+        <v>95</v>
+      </c>
+    </row>
+    <row r="97" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A97">
+        <v>96</v>
+      </c>
+    </row>
+    <row r="98" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A98">
+        <v>97</v>
+      </c>
+    </row>
+    <row r="99" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A99">
+        <v>98</v>
+      </c>
+    </row>
+    <row r="100" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A100">
+        <v>99</v>
+      </c>
+    </row>
+    <row r="101" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A101">
+        <v>100</v>
+      </c>
+    </row>
+    <row r="102" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A102">
+        <v>101</v>
+      </c>
+    </row>
+    <row r="103" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A103">
+        <v>102</v>
+      </c>
+    </row>
+    <row r="104" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A104">
+        <v>103</v>
+      </c>
+    </row>
+    <row r="105" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A105">
+        <v>104</v>
+      </c>
+    </row>
+    <row r="106" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A106">
+        <v>105</v>
+      </c>
+    </row>
+    <row r="107" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A107">
+        <v>106</v>
+      </c>
+    </row>
+    <row r="108" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A108">
+        <v>107</v>
+      </c>
+    </row>
+    <row r="109" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A109">
+        <v>108</v>
+      </c>
+    </row>
+    <row r="110" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A110">
+        <v>109</v>
+      </c>
+    </row>
+    <row r="111" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A111">
+        <v>110</v>
+      </c>
+    </row>
+    <row r="112" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A112">
+        <v>111</v>
+      </c>
+    </row>
+    <row r="113" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A113">
+        <v>112</v>
+      </c>
+    </row>
+    <row r="114" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A114">
+        <v>113</v>
+      </c>
+    </row>
+    <row r="115" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A115">
+        <v>114</v>
+      </c>
+    </row>
+    <row r="116" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A116">
+        <v>115</v>
+      </c>
+    </row>
+    <row r="117" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A117">
+        <v>116</v>
+      </c>
+    </row>
+    <row r="118" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A118">
+        <v>117</v>
+      </c>
+    </row>
+    <row r="119" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A119">
+        <v>118</v>
+      </c>
+    </row>
+    <row r="120" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A120">
+        <v>119</v>
+      </c>
+    </row>
+    <row r="121" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A121">
+        <v>120</v>
+      </c>
+    </row>
+    <row r="122" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A122">
+        <v>121</v>
+      </c>
+    </row>
+    <row r="123" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A123">
+        <v>122</v>
+      </c>
+    </row>
+    <row r="124" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A124">
+        <v>123</v>
+      </c>
+    </row>
+    <row r="125" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A125">
+        <v>124</v>
+      </c>
+    </row>
+    <row r="126" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A126">
+        <v>125</v>
+      </c>
+    </row>
+    <row r="127" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A127">
+        <v>126</v>
+      </c>
+    </row>
+    <row r="128" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A128">
+        <v>127</v>
+      </c>
+    </row>
+    <row r="129" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A129">
+        <v>128</v>
+      </c>
+    </row>
+    <row r="130" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A130">
+        <v>129</v>
+      </c>
+    </row>
+    <row r="131" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A131">
+        <v>130</v>
+      </c>
+    </row>
+    <row r="132" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A132">
+        <v>131</v>
+      </c>
+    </row>
+    <row r="133" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A133">
+        <v>132</v>
+      </c>
+    </row>
+    <row r="134" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A134">
+        <v>133</v>
+      </c>
+    </row>
+    <row r="135" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A135">
+        <v>134</v>
+      </c>
+    </row>
+    <row r="136" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A136">
+        <v>135</v>
+      </c>
+    </row>
+    <row r="137" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A137">
+        <v>136</v>
+      </c>
+    </row>
+    <row r="138" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A138">
+        <v>137</v>
+      </c>
+    </row>
+    <row r="139" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A139">
+        <v>138</v>
+      </c>
+    </row>
+    <row r="140" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A140">
+        <v>139</v>
+      </c>
+    </row>
+    <row r="141" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A141">
+        <v>140</v>
+      </c>
+    </row>
+    <row r="142" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A142">
+        <v>141</v>
+      </c>
+    </row>
+    <row r="143" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A143">
+        <v>142</v>
+      </c>
+    </row>
+    <row r="144" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A144">
+        <v>143</v>
+      </c>
+    </row>
+    <row r="145" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A145">
+        <v>144</v>
+      </c>
+    </row>
+    <row r="146" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A146">
+        <v>145</v>
+      </c>
+    </row>
+    <row r="147" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A147">
+        <v>146</v>
+      </c>
+    </row>
+    <row r="148" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A148">
+        <v>147</v>
+      </c>
+    </row>
+    <row r="149" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A149">
+        <v>148</v>
+      </c>
+    </row>
+    <row r="150" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A150">
+        <v>149</v>
+      </c>
+    </row>
+    <row r="151" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A151">
+        <v>150</v>
+      </c>
+    </row>
   </sheetData>
+  <hyperlinks>
+    <hyperlink ref="E90" r:id="rId1" display="mailto:miriam.sotov@redsalud.gob.cl" xr:uid="{CA864F29-52B2-43C7-A13E-76AEC8A49A4F}"/>
+    <hyperlink ref="G90" r:id="rId2" display="mailto:sandra.felipe@redsalud.gob.cl" xr:uid="{E976CC02-5359-4441-A979-BD71659626F9}"/>
+    <hyperlink ref="E91" r:id="rId3" display="mailto:mariela.gallardo@redsalud.gob.cl" xr:uid="{9C732FB4-A61F-4E39-B898-750F2EC775F1}"/>
+    <hyperlink ref="G91" r:id="rId4" display="mailto:iris.reyes@redsalud.gob.cl" xr:uid="{C4E3479B-2B05-4DD8-8E11-9D8BF2B85E31}"/>
+    <hyperlink ref="E92" r:id="rId5" display="mailto:valentina.molinah@redsalud.gob.cl" xr:uid="{C1ADBA44-5B7A-4977-AABE-11063BE1B6A7}"/>
+    <hyperlink ref="G92" r:id="rId6" display="mailto:iris.reyes@redsalud.gob.cl" xr:uid="{D04DDA16-E51A-4689-BBD7-423B1C3B374F}"/>
+    <hyperlink ref="E93" r:id="rId7" display="mailto:ariel.davila.q@redsalud.gob.cl" xr:uid="{EC233077-E60B-496D-AE88-C023286395AA}"/>
+    <hyperlink ref="G93" r:id="rId8" display="mailto:iris.reyes@redsalud.gob.cl" xr:uid="{83E83D38-31B5-4021-9A85-A21840781BD6}"/>
+    <hyperlink ref="E94" r:id="rId9" display="mailto:veronica.perez.gutierrez@redsalud.gob.cl" xr:uid="{FA6F0642-EBF9-4CD6-9C47-58B1F0F3E6C0}"/>
+    <hyperlink ref="G94" r:id="rId10" display="mailto:adriana.toledo@redsalud.gob.cl" xr:uid="{CD766FCC-3306-4798-96D5-1B84D28ECDC6}"/>
+    <hyperlink ref="E95" r:id="rId11" display="mailto:romy.geissbuhler@redsalud.gob.cl" xr:uid="{7D4D5B0A-0E35-49DA-AA2E-78A73F7C081E}"/>
+    <hyperlink ref="G95" r:id="rId12" display="mailto:marisol.lara@redsalud.gob.cl" xr:uid="{49F93AE7-78F6-409A-802B-D4EFCB8ABFD3}"/>
+  </hyperlinks>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
 </file>
--- a/2- BB.DD. SERVICIOS Y UNIDADES/BBDD SERVICIOS Y UNIDADES.xlsx
+++ b/2- BB.DD. SERVICIOS Y UNIDADES/BBDD SERVICIOS Y UNIDADES.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30326"/>
-  <workbookPr defaultThemeVersion="202300"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="24334"/>
+  <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\IPLACEX\Año 2\PRÁCTICA IPLACEX\PLATAFORMA PASANTÍAS\GITHUB\2- BB.DD. SERVICIOS Y UNIDADES\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="E:\IPLACEX\Año 2\PRÁCTICA IPLACEX\PLATAFORMA PASANTÍAS\GITHUB\2- BB.DD. SERVICIOS Y UNIDADES\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{D7EB8174-AF74-425B-93AB-6477E2A8F7EC}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{B37D8AE0-69A6-43DD-AEF4-BD853A445F38}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-28920" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{7936E908-9EDA-4102-87A8-C4382552261F}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="21840" windowHeight="13140" xr2:uid="{7936E908-9EDA-4102-87A8-C4382552261F}"/>
   </bookViews>
   <sheets>
     <sheet name="Hoja1" sheetId="1" r:id="rId1"/>
@@ -27,8 +27,6 @@
         <xcalcf:feature name="microsoft.com:FV"/>
         <xcalcf:feature name="microsoft.com:CNMTM"/>
         <xcalcf:feature name="microsoft.com:LET_WF"/>
-        <xcalcf:feature name="microsoft.com:LAMBDA_WF"/>
-        <xcalcf:feature name="microsoft.com:ARRAYTEXT_WF"/>
       </xcalcf:calcFeatures>
     </ext>
     <ext xmlns:xlwcv="http://schemas.microsoft.com/office/spreadsheetml/2024/workbookCompatibilityVersion" uri="{D14903EA-33C4-47F7-8F05-3474C54BE107}">
@@ -39,7 +37,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="572" uniqueCount="357">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="602" uniqueCount="379">
   <si>
     <t>id</t>
   </si>
@@ -1110,13 +1108,79 @@
   </si>
   <si>
     <t>victor. aliste.c@redsalud.gob.cl</t>
+  </si>
+  <si>
+    <t>estadística</t>
+  </si>
+  <si>
+    <t>tommy farías núñez</t>
+  </si>
+  <si>
+    <t>tommy.farias@redsalud.gob.cl</t>
+  </si>
+  <si>
+    <t>soledad flores urbina</t>
+  </si>
+  <si>
+    <t>soledad.flores@redsalud.gob.cl</t>
+  </si>
+  <si>
+    <t>planificación y control de gestión</t>
+  </si>
+  <si>
+    <t>jessica fonseca figueroa</t>
+  </si>
+  <si>
+    <t>jessica.fonseca@redsalud.gob.cl</t>
+  </si>
+  <si>
+    <t>grd</t>
+  </si>
+  <si>
+    <t>marlene pavez muñoz</t>
+  </si>
+  <si>
+    <t>marlene.pavez@redsalud.gob.cl</t>
+  </si>
+  <si>
+    <t>paola rodríguez rivera</t>
+  </si>
+  <si>
+    <t>paola.rodriguezr@redsalud.gob.cl</t>
+  </si>
+  <si>
+    <t>informática</t>
+  </si>
+  <si>
+    <t>irma matus de la parra becerra</t>
+  </si>
+  <si>
+    <t>irma.matusdelaparra@redsalud.gob.cl</t>
+  </si>
+  <si>
+    <t>violeta sepúlveda bravo</t>
+  </si>
+  <si>
+    <t>violeta.sepulveda@redsalud.gob.cl</t>
+  </si>
+  <si>
+    <t>sigges</t>
+  </si>
+  <si>
+    <t>josé luis espinoza</t>
+  </si>
+  <si>
+    <t>jose.espinoza.d@redsalud.gob.cl</t>
+  </si>
+  <si>
+    <t>desarrollo estratégico</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="1" x14ac:knownFonts="1">
+  <fonts count="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -1492,18 +1556,18 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{37800E50-6288-4855-903E-7D1C9ED078D0}">
   <dimension ref="A1:H151"/>
-  <sheetFormatPr baseColWidth="10" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr baseColWidth="10" defaultRowHeight="14.25"/>
   <cols>
     <col min="1" max="1" width="4" bestFit="1" customWidth="1"/>
     <col min="2" max="2" width="35" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="45.140625" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="33.140625" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="45.125" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="33.125" bestFit="1" customWidth="1"/>
     <col min="5" max="5" width="40" bestFit="1" customWidth="1"/>
-    <col min="6" max="6" width="32.7109375" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="32.75" bestFit="1" customWidth="1"/>
     <col min="7" max="7" width="34" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:8">
       <c r="A1" t="s">
         <v>0</v>
       </c>
@@ -1529,7 +1593,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="2" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:8">
       <c r="A2">
         <v>1</v>
       </c>
@@ -1552,7 +1616,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="3" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="3" spans="1:8">
       <c r="A3">
         <v>2</v>
       </c>
@@ -1575,7 +1639,7 @@
         <v>13</v>
       </c>
     </row>
-    <row r="4" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="4" spans="1:8">
       <c r="A4">
         <v>3</v>
       </c>
@@ -1598,7 +1662,7 @@
         <v>16</v>
       </c>
     </row>
-    <row r="5" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="5" spans="1:8">
       <c r="A5">
         <v>4</v>
       </c>
@@ -1621,7 +1685,7 @@
         <v>19</v>
       </c>
     </row>
-    <row r="6" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="6" spans="1:8">
       <c r="A6">
         <v>5</v>
       </c>
@@ -1644,7 +1708,7 @@
         <v>22</v>
       </c>
     </row>
-    <row r="7" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="7" spans="1:8">
       <c r="A7">
         <v>6</v>
       </c>
@@ -1667,7 +1731,7 @@
         <v>26</v>
       </c>
     </row>
-    <row r="8" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="8" spans="1:8">
       <c r="A8">
         <v>7</v>
       </c>
@@ -1690,7 +1754,7 @@
         <v>30</v>
       </c>
     </row>
-    <row r="9" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="9" spans="1:8">
       <c r="A9">
         <v>8</v>
       </c>
@@ -1713,7 +1777,7 @@
         <v>34</v>
       </c>
     </row>
-    <row r="10" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="10" spans="1:8">
       <c r="A10">
         <v>9</v>
       </c>
@@ -1736,7 +1800,7 @@
         <v>37</v>
       </c>
     </row>
-    <row r="11" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="11" spans="1:8">
       <c r="A11">
         <v>10</v>
       </c>
@@ -1759,7 +1823,7 @@
         <v>41</v>
       </c>
     </row>
-    <row r="12" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="12" spans="1:8">
       <c r="A12">
         <v>11</v>
       </c>
@@ -1782,7 +1846,7 @@
         <v>44</v>
       </c>
     </row>
-    <row r="13" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="13" spans="1:8">
       <c r="A13">
         <v>12</v>
       </c>
@@ -1805,7 +1869,7 @@
         <v>48</v>
       </c>
     </row>
-    <row r="14" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="14" spans="1:8">
       <c r="A14">
         <v>13</v>
       </c>
@@ -1828,7 +1892,7 @@
         <v>52</v>
       </c>
     </row>
-    <row r="15" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="15" spans="1:8">
       <c r="A15">
         <v>14</v>
       </c>
@@ -1851,7 +1915,7 @@
         <v>44</v>
       </c>
     </row>
-    <row r="16" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="16" spans="1:8">
       <c r="A16">
         <v>15</v>
       </c>
@@ -1874,7 +1938,7 @@
         <v>44</v>
       </c>
     </row>
-    <row r="17" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="17" spans="1:7">
       <c r="A17">
         <v>16</v>
       </c>
@@ -1897,7 +1961,7 @@
         <v>44</v>
       </c>
     </row>
-    <row r="18" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="18" spans="1:7">
       <c r="A18">
         <v>17</v>
       </c>
@@ -1920,7 +1984,7 @@
         <v>44</v>
       </c>
     </row>
-    <row r="19" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="19" spans="1:7">
       <c r="A19">
         <v>18</v>
       </c>
@@ -1943,7 +2007,7 @@
         <v>44</v>
       </c>
     </row>
-    <row r="20" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="20" spans="1:7">
       <c r="A20">
         <v>19</v>
       </c>
@@ -1966,7 +2030,7 @@
         <v>44</v>
       </c>
     </row>
-    <row r="21" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="21" spans="1:7">
       <c r="A21">
         <v>20</v>
       </c>
@@ -1989,7 +2053,7 @@
         <v>44</v>
       </c>
     </row>
-    <row r="22" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="22" spans="1:7">
       <c r="A22">
         <v>21</v>
       </c>
@@ -2012,7 +2076,7 @@
         <v>44</v>
       </c>
     </row>
-    <row r="23" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="23" spans="1:7">
       <c r="A23">
         <v>22</v>
       </c>
@@ -2035,7 +2099,7 @@
         <v>44</v>
       </c>
     </row>
-    <row r="24" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="24" spans="1:7">
       <c r="A24">
         <v>23</v>
       </c>
@@ -2058,7 +2122,7 @@
         <v>192</v>
       </c>
     </row>
-    <row r="25" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="25" spans="1:7">
       <c r="A25">
         <v>24</v>
       </c>
@@ -2081,7 +2145,7 @@
         <v>86</v>
       </c>
     </row>
-    <row r="26" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="26" spans="1:7">
       <c r="A26">
         <v>25</v>
       </c>
@@ -2104,7 +2168,7 @@
         <v>90</v>
       </c>
     </row>
-    <row r="27" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="27" spans="1:7">
       <c r="A27">
         <v>26</v>
       </c>
@@ -2127,7 +2191,7 @@
         <v>94</v>
       </c>
     </row>
-    <row r="28" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="28" spans="1:7">
       <c r="A28">
         <v>27</v>
       </c>
@@ -2150,7 +2214,7 @@
         <v>98</v>
       </c>
     </row>
-    <row r="29" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="29" spans="1:7">
       <c r="A29">
         <v>28</v>
       </c>
@@ -2173,7 +2237,7 @@
         <v>44</v>
       </c>
     </row>
-    <row r="30" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="30" spans="1:7">
       <c r="A30">
         <v>29</v>
       </c>
@@ -2196,7 +2260,7 @@
         <v>102</v>
       </c>
     </row>
-    <row r="31" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="31" spans="1:7">
       <c r="A31">
         <v>30</v>
       </c>
@@ -2219,7 +2283,7 @@
         <v>44</v>
       </c>
     </row>
-    <row r="32" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="32" spans="1:7">
       <c r="A32">
         <v>31</v>
       </c>
@@ -2242,7 +2306,7 @@
         <v>109</v>
       </c>
     </row>
-    <row r="33" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="33" spans="1:7">
       <c r="A33">
         <v>32</v>
       </c>
@@ -2265,7 +2329,7 @@
         <v>113</v>
       </c>
     </row>
-    <row r="34" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="34" spans="1:7">
       <c r="A34">
         <v>33</v>
       </c>
@@ -2288,7 +2352,7 @@
         <v>118</v>
       </c>
     </row>
-    <row r="35" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="35" spans="1:7">
       <c r="A35">
         <v>34</v>
       </c>
@@ -2311,7 +2375,7 @@
         <v>122</v>
       </c>
     </row>
-    <row r="36" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="36" spans="1:7">
       <c r="A36">
         <v>35</v>
       </c>
@@ -2334,7 +2398,7 @@
         <v>126</v>
       </c>
     </row>
-    <row r="37" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="37" spans="1:7">
       <c r="A37">
         <v>36</v>
       </c>
@@ -2357,7 +2421,7 @@
         <v>130</v>
       </c>
     </row>
-    <row r="38" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="38" spans="1:7">
       <c r="A38">
         <v>37</v>
       </c>
@@ -2380,7 +2444,7 @@
         <v>134</v>
       </c>
     </row>
-    <row r="39" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="39" spans="1:7">
       <c r="A39">
         <v>38</v>
       </c>
@@ -2403,7 +2467,7 @@
         <v>139</v>
       </c>
     </row>
-    <row r="40" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="40" spans="1:7">
       <c r="A40">
         <v>39</v>
       </c>
@@ -2426,7 +2490,7 @@
         <v>174</v>
       </c>
     </row>
-    <row r="41" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="41" spans="1:7">
       <c r="A41">
         <v>40</v>
       </c>
@@ -2449,7 +2513,7 @@
         <v>179</v>
       </c>
     </row>
-    <row r="42" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="42" spans="1:7">
       <c r="A42">
         <v>41</v>
       </c>
@@ -2472,7 +2536,7 @@
         <v>184</v>
       </c>
     </row>
-    <row r="43" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="43" spans="1:7">
       <c r="A43">
         <v>42</v>
       </c>
@@ -2495,7 +2559,7 @@
         <v>82</v>
       </c>
     </row>
-    <row r="44" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="44" spans="1:7">
       <c r="A44">
         <v>43</v>
       </c>
@@ -2518,7 +2582,7 @@
         <v>82</v>
       </c>
     </row>
-    <row r="45" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="45" spans="1:7">
       <c r="A45">
         <v>44</v>
       </c>
@@ -2541,7 +2605,7 @@
         <v>82</v>
       </c>
     </row>
-    <row r="46" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="46" spans="1:7">
       <c r="A46">
         <v>45</v>
       </c>
@@ -2564,7 +2628,7 @@
         <v>82</v>
       </c>
     </row>
-    <row r="47" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="47" spans="1:7">
       <c r="A47">
         <v>46</v>
       </c>
@@ -2587,7 +2651,7 @@
         <v>82</v>
       </c>
     </row>
-    <row r="48" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="48" spans="1:7">
       <c r="A48">
         <v>47</v>
       </c>
@@ -2610,7 +2674,7 @@
         <v>82</v>
       </c>
     </row>
-    <row r="49" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="49" spans="1:7">
       <c r="A49">
         <v>48</v>
       </c>
@@ -2633,7 +2697,7 @@
         <v>82</v>
       </c>
     </row>
-    <row r="50" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="50" spans="1:7">
       <c r="A50">
         <v>49</v>
       </c>
@@ -2656,7 +2720,7 @@
         <v>82</v>
       </c>
     </row>
-    <row r="51" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="51" spans="1:7">
       <c r="A51">
         <v>50</v>
       </c>
@@ -2679,7 +2743,7 @@
         <v>82</v>
       </c>
     </row>
-    <row r="52" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="52" spans="1:7">
       <c r="A52">
         <v>51</v>
       </c>
@@ -2702,7 +2766,7 @@
         <v>82</v>
       </c>
     </row>
-    <row r="53" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="53" spans="1:7">
       <c r="A53">
         <v>52</v>
       </c>
@@ -2725,7 +2789,7 @@
         <v>82</v>
       </c>
     </row>
-    <row r="54" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="54" spans="1:7">
       <c r="A54">
         <v>53</v>
       </c>
@@ -2748,7 +2812,7 @@
         <v>82</v>
       </c>
     </row>
-    <row r="55" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="55" spans="1:7">
       <c r="A55">
         <v>54</v>
       </c>
@@ -2771,7 +2835,7 @@
         <v>82</v>
       </c>
     </row>
-    <row r="56" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="56" spans="1:7">
       <c r="A56">
         <v>55</v>
       </c>
@@ -2794,7 +2858,7 @@
         <v>82</v>
       </c>
     </row>
-    <row r="57" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="57" spans="1:7">
       <c r="A57">
         <v>56</v>
       </c>
@@ -2817,7 +2881,7 @@
         <v>82</v>
       </c>
     </row>
-    <row r="58" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="58" spans="1:7">
       <c r="A58">
         <v>57</v>
       </c>
@@ -2840,7 +2904,7 @@
         <v>82</v>
       </c>
     </row>
-    <row r="59" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="59" spans="1:7">
       <c r="A59">
         <v>58</v>
       </c>
@@ -2863,7 +2927,7 @@
         <v>82</v>
       </c>
     </row>
-    <row r="60" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="60" spans="1:7">
       <c r="A60">
         <v>59</v>
       </c>
@@ -2886,7 +2950,7 @@
         <v>82</v>
       </c>
     </row>
-    <row r="61" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="61" spans="1:7">
       <c r="A61">
         <v>60</v>
       </c>
@@ -2909,7 +2973,7 @@
         <v>82</v>
       </c>
     </row>
-    <row r="62" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="62" spans="1:7">
       <c r="A62">
         <v>61</v>
       </c>
@@ -2932,7 +2996,7 @@
         <v>82</v>
       </c>
     </row>
-    <row r="63" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="63" spans="1:7">
       <c r="A63">
         <v>62</v>
       </c>
@@ -2955,7 +3019,7 @@
         <v>82</v>
       </c>
     </row>
-    <row r="64" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="64" spans="1:7">
       <c r="A64">
         <v>63</v>
       </c>
@@ -2978,7 +3042,7 @@
         <v>82</v>
       </c>
     </row>
-    <row r="65" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="65" spans="1:7">
       <c r="A65">
         <v>64</v>
       </c>
@@ -3001,7 +3065,7 @@
         <v>82</v>
       </c>
     </row>
-    <row r="66" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="66" spans="1:7">
       <c r="A66">
         <v>65</v>
       </c>
@@ -3024,7 +3088,7 @@
         <v>82</v>
       </c>
     </row>
-    <row r="67" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="67" spans="1:7">
       <c r="A67">
         <v>66</v>
       </c>
@@ -3047,7 +3111,7 @@
         <v>82</v>
       </c>
     </row>
-    <row r="68" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="68" spans="1:7">
       <c r="A68">
         <v>67</v>
       </c>
@@ -3070,7 +3134,7 @@
         <v>82</v>
       </c>
     </row>
-    <row r="69" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="69" spans="1:7">
       <c r="A69">
         <v>68</v>
       </c>
@@ -3093,7 +3157,7 @@
         <v>82</v>
       </c>
     </row>
-    <row r="70" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="70" spans="1:7">
       <c r="A70">
         <v>69</v>
       </c>
@@ -3116,7 +3180,7 @@
         <v>82</v>
       </c>
     </row>
-    <row r="71" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="71" spans="1:7">
       <c r="A71">
         <v>70</v>
       </c>
@@ -3139,7 +3203,7 @@
         <v>82</v>
       </c>
     </row>
-    <row r="72" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="72" spans="1:7">
       <c r="A72">
         <v>71</v>
       </c>
@@ -3162,7 +3226,7 @@
         <v>82</v>
       </c>
     </row>
-    <row r="73" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="73" spans="1:7">
       <c r="A73">
         <v>72</v>
       </c>
@@ -3185,7 +3249,7 @@
         <v>82</v>
       </c>
     </row>
-    <row r="74" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="74" spans="1:7">
       <c r="A74">
         <v>73</v>
       </c>
@@ -3208,7 +3272,7 @@
         <v>82</v>
       </c>
     </row>
-    <row r="75" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="75" spans="1:7">
       <c r="A75">
         <v>74</v>
       </c>
@@ -3231,7 +3295,7 @@
         <v>82</v>
       </c>
     </row>
-    <row r="76" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="76" spans="1:7">
       <c r="A76">
         <v>75</v>
       </c>
@@ -3254,7 +3318,7 @@
         <v>82</v>
       </c>
     </row>
-    <row r="77" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="77" spans="1:7">
       <c r="A77">
         <v>76</v>
       </c>
@@ -3277,7 +3341,7 @@
         <v>82</v>
       </c>
     </row>
-    <row r="78" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="78" spans="1:7">
       <c r="A78">
         <v>77</v>
       </c>
@@ -3300,7 +3364,7 @@
         <v>82</v>
       </c>
     </row>
-    <row r="79" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="79" spans="1:7">
       <c r="A79">
         <v>78</v>
       </c>
@@ -3323,7 +3387,7 @@
         <v>82</v>
       </c>
     </row>
-    <row r="80" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="80" spans="1:7">
       <c r="A80">
         <v>79</v>
       </c>
@@ -3346,7 +3410,7 @@
         <v>82</v>
       </c>
     </row>
-    <row r="81" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="81" spans="1:7">
       <c r="A81">
         <v>80</v>
       </c>
@@ -3369,7 +3433,7 @@
         <v>82</v>
       </c>
     </row>
-    <row r="82" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="82" spans="1:7">
       <c r="A82">
         <v>81</v>
       </c>
@@ -3392,7 +3456,7 @@
         <v>82</v>
       </c>
     </row>
-    <row r="83" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="83" spans="1:7">
       <c r="A83">
         <v>82</v>
       </c>
@@ -3415,7 +3479,7 @@
         <v>82</v>
       </c>
     </row>
-    <row r="84" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="84" spans="1:7">
       <c r="A84">
         <v>83</v>
       </c>
@@ -3438,7 +3502,7 @@
         <v>82</v>
       </c>
     </row>
-    <row r="85" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="85" spans="1:7">
       <c r="A85">
         <v>84</v>
       </c>
@@ -3461,7 +3525,7 @@
         <v>82</v>
       </c>
     </row>
-    <row r="86" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="86" spans="1:7">
       <c r="A86">
         <v>85</v>
       </c>
@@ -3484,7 +3548,7 @@
         <v>82</v>
       </c>
     </row>
-    <row r="87" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="87" spans="1:7">
       <c r="A87">
         <v>86</v>
       </c>
@@ -3507,7 +3571,7 @@
         <v>82</v>
       </c>
     </row>
-    <row r="88" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="88" spans="1:7">
       <c r="A88">
         <v>87</v>
       </c>
@@ -3530,7 +3594,7 @@
         <v>82</v>
       </c>
     </row>
-    <row r="89" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="89" spans="1:7">
       <c r="A89">
         <v>88</v>
       </c>
@@ -3553,7 +3617,7 @@
         <v>82</v>
       </c>
     </row>
-    <row r="90" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="90" spans="1:7">
       <c r="A90">
         <v>89</v>
       </c>
@@ -3576,7 +3640,7 @@
         <v>333</v>
       </c>
     </row>
-    <row r="91" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="91" spans="1:7">
       <c r="A91">
         <v>90</v>
       </c>
@@ -3599,7 +3663,7 @@
         <v>338</v>
       </c>
     </row>
-    <row r="92" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="92" spans="1:7">
       <c r="A92">
         <v>91</v>
       </c>
@@ -3622,7 +3686,7 @@
         <v>338</v>
       </c>
     </row>
-    <row r="93" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="93" spans="1:7">
       <c r="A93">
         <v>92</v>
       </c>
@@ -3645,7 +3709,7 @@
         <v>338</v>
       </c>
     </row>
-    <row r="94" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="94" spans="1:7">
       <c r="A94">
         <v>93</v>
       </c>
@@ -3668,7 +3732,7 @@
         <v>349</v>
       </c>
     </row>
-    <row r="95" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="95" spans="1:7">
       <c r="A95">
         <v>94</v>
       </c>
@@ -3691,282 +3755,372 @@
         <v>354</v>
       </c>
     </row>
-    <row r="96" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="96" spans="1:7">
       <c r="A96">
         <v>95</v>
       </c>
-    </row>
-    <row r="97" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="B96" t="s">
+        <v>378</v>
+      </c>
+      <c r="C96" t="s">
+        <v>357</v>
+      </c>
+      <c r="D96" t="s">
+        <v>358</v>
+      </c>
+      <c r="E96" t="s">
+        <v>359</v>
+      </c>
+      <c r="F96" t="s">
+        <v>360</v>
+      </c>
+      <c r="G96" t="s">
+        <v>361</v>
+      </c>
+    </row>
+    <row r="97" spans="1:7">
       <c r="A97">
         <v>96</v>
       </c>
-    </row>
-    <row r="98" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="B97" t="s">
+        <v>378</v>
+      </c>
+      <c r="C97" t="s">
+        <v>362</v>
+      </c>
+      <c r="D97" t="s">
+        <v>363</v>
+      </c>
+      <c r="E97" t="s">
+        <v>364</v>
+      </c>
+      <c r="F97" t="s">
+        <v>44</v>
+      </c>
+      <c r="G97" t="s">
+        <v>44</v>
+      </c>
+    </row>
+    <row r="98" spans="1:7">
       <c r="A98">
         <v>97</v>
       </c>
-    </row>
-    <row r="99" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="B98" t="s">
+        <v>378</v>
+      </c>
+      <c r="C98" t="s">
+        <v>365</v>
+      </c>
+      <c r="D98" t="s">
+        <v>366</v>
+      </c>
+      <c r="E98" t="s">
+        <v>367</v>
+      </c>
+      <c r="F98" t="s">
+        <v>368</v>
+      </c>
+      <c r="G98" t="s">
+        <v>369</v>
+      </c>
+    </row>
+    <row r="99" spans="1:7">
       <c r="A99">
         <v>98</v>
       </c>
-    </row>
-    <row r="100" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="B99" t="s">
+        <v>378</v>
+      </c>
+      <c r="C99" t="s">
+        <v>370</v>
+      </c>
+      <c r="D99" t="s">
+        <v>371</v>
+      </c>
+      <c r="E99" t="s">
+        <v>372</v>
+      </c>
+      <c r="F99" t="s">
+        <v>373</v>
+      </c>
+      <c r="G99" t="s">
+        <v>374</v>
+      </c>
+    </row>
+    <row r="100" spans="1:7">
       <c r="A100">
         <v>99</v>
       </c>
-    </row>
-    <row r="101" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="B100" t="s">
+        <v>378</v>
+      </c>
+      <c r="C100" t="s">
+        <v>375</v>
+      </c>
+      <c r="D100" t="s">
+        <v>376</v>
+      </c>
+      <c r="E100" t="s">
+        <v>377</v>
+      </c>
+      <c r="F100" t="s">
+        <v>44</v>
+      </c>
+      <c r="G100" t="s">
+        <v>44</v>
+      </c>
+    </row>
+    <row r="101" spans="1:7">
       <c r="A101">
         <v>100</v>
       </c>
     </row>
-    <row r="102" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="102" spans="1:7">
       <c r="A102">
         <v>101</v>
       </c>
     </row>
-    <row r="103" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="103" spans="1:7">
       <c r="A103">
         <v>102</v>
       </c>
     </row>
-    <row r="104" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="104" spans="1:7">
       <c r="A104">
         <v>103</v>
       </c>
     </row>
-    <row r="105" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="105" spans="1:7">
       <c r="A105">
         <v>104</v>
       </c>
     </row>
-    <row r="106" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="106" spans="1:7">
       <c r="A106">
         <v>105</v>
       </c>
     </row>
-    <row r="107" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="107" spans="1:7">
       <c r="A107">
         <v>106</v>
       </c>
     </row>
-    <row r="108" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="108" spans="1:7">
       <c r="A108">
         <v>107</v>
       </c>
     </row>
-    <row r="109" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="109" spans="1:7">
       <c r="A109">
         <v>108</v>
       </c>
     </row>
-    <row r="110" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="110" spans="1:7">
       <c r="A110">
         <v>109</v>
       </c>
     </row>
-    <row r="111" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="111" spans="1:7">
       <c r="A111">
         <v>110</v>
       </c>
     </row>
-    <row r="112" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="112" spans="1:7">
       <c r="A112">
         <v>111</v>
       </c>
     </row>
-    <row r="113" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="113" spans="1:1">
       <c r="A113">
         <v>112</v>
       </c>
     </row>
-    <row r="114" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="114" spans="1:1">
       <c r="A114">
         <v>113</v>
       </c>
     </row>
-    <row r="115" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="115" spans="1:1">
       <c r="A115">
         <v>114</v>
       </c>
     </row>
-    <row r="116" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="116" spans="1:1">
       <c r="A116">
         <v>115</v>
       </c>
     </row>
-    <row r="117" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="117" spans="1:1">
       <c r="A117">
         <v>116</v>
       </c>
     </row>
-    <row r="118" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="118" spans="1:1">
       <c r="A118">
         <v>117</v>
       </c>
     </row>
-    <row r="119" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="119" spans="1:1">
       <c r="A119">
         <v>118</v>
       </c>
     </row>
-    <row r="120" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="120" spans="1:1">
       <c r="A120">
         <v>119</v>
       </c>
     </row>
-    <row r="121" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="121" spans="1:1">
       <c r="A121">
         <v>120</v>
       </c>
     </row>
-    <row r="122" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="122" spans="1:1">
       <c r="A122">
         <v>121</v>
       </c>
     </row>
-    <row r="123" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="123" spans="1:1">
       <c r="A123">
         <v>122</v>
       </c>
     </row>
-    <row r="124" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="124" spans="1:1">
       <c r="A124">
         <v>123</v>
       </c>
     </row>
-    <row r="125" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="125" spans="1:1">
       <c r="A125">
         <v>124</v>
       </c>
     </row>
-    <row r="126" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="126" spans="1:1">
       <c r="A126">
         <v>125</v>
       </c>
     </row>
-    <row r="127" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="127" spans="1:1">
       <c r="A127">
         <v>126</v>
       </c>
     </row>
-    <row r="128" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="128" spans="1:1">
       <c r="A128">
         <v>127</v>
       </c>
     </row>
-    <row r="129" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="129" spans="1:1">
       <c r="A129">
         <v>128</v>
       </c>
     </row>
-    <row r="130" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="130" spans="1:1">
       <c r="A130">
         <v>129</v>
       </c>
     </row>
-    <row r="131" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="131" spans="1:1">
       <c r="A131">
         <v>130</v>
       </c>
     </row>
-    <row r="132" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="132" spans="1:1">
       <c r="A132">
         <v>131</v>
       </c>
     </row>
-    <row r="133" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="133" spans="1:1">
       <c r="A133">
         <v>132</v>
       </c>
     </row>
-    <row r="134" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="134" spans="1:1">
       <c r="A134">
         <v>133</v>
       </c>
     </row>
-    <row r="135" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="135" spans="1:1">
       <c r="A135">
         <v>134</v>
       </c>
     </row>
-    <row r="136" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="136" spans="1:1">
       <c r="A136">
         <v>135</v>
       </c>
     </row>
-    <row r="137" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="137" spans="1:1">
       <c r="A137">
         <v>136</v>
       </c>
     </row>
-    <row r="138" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="138" spans="1:1">
       <c r="A138">
         <v>137</v>
       </c>
     </row>
-    <row r="139" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="139" spans="1:1">
       <c r="A139">
         <v>138</v>
       </c>
     </row>
-    <row r="140" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="140" spans="1:1">
       <c r="A140">
         <v>139</v>
       </c>
     </row>
-    <row r="141" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="141" spans="1:1">
       <c r="A141">
         <v>140</v>
       </c>
     </row>
-    <row r="142" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="142" spans="1:1">
       <c r="A142">
         <v>141</v>
       </c>
     </row>
-    <row r="143" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="143" spans="1:1">
       <c r="A143">
         <v>142</v>
       </c>
     </row>
-    <row r="144" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="144" spans="1:1">
       <c r="A144">
         <v>143</v>
       </c>
     </row>
-    <row r="145" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="145" spans="1:1">
       <c r="A145">
         <v>144</v>
       </c>
     </row>
-    <row r="146" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="146" spans="1:1">
       <c r="A146">
         <v>145</v>
       </c>
     </row>
-    <row r="147" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="147" spans="1:1">
       <c r="A147">
         <v>146</v>
       </c>
     </row>
-    <row r="148" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="148" spans="1:1">
       <c r="A148">
         <v>147</v>
       </c>
     </row>
-    <row r="149" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="149" spans="1:1">
       <c r="A149">
         <v>148</v>
       </c>
     </row>
-    <row r="150" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="150" spans="1:1">
       <c r="A150">
         <v>149</v>
       </c>
     </row>
-    <row r="151" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="151" spans="1:1">
       <c r="A151">
         <v>150</v>
       </c>
